--- a/prix/levis.xlsx
+++ b/prix/levis.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\site-internet\peintures\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7624A490-26F7-472E-8B69-F8F130F09345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E34789-8F82-4DA8-9209-5A49BBCCBCC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -1672,7 +1672,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="36">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -1752,7 +1752,7 @@
         <v>8</v>
       </c>
       <c r="F6" s="36">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1792,7 +1792,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="36">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -1932,7 +1932,7 @@
         <v>26</v>
       </c>
       <c r="F15" s="36">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -1992,7 +1992,7 @@
         <v>32</v>
       </c>
       <c r="F18" s="36">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -2243,13 +2243,13 @@
         <v>283</v>
       </c>
       <c r="D31" s="37">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F31" s="36">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -2309,7 +2309,7 @@
         <v>64</v>
       </c>
       <c r="F34" s="36">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -2329,7 +2329,7 @@
         <v>66</v>
       </c>
       <c r="F35" s="36">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -2369,7 +2369,7 @@
         <v>70</v>
       </c>
       <c r="F37" s="36">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -3377,13 +3377,13 @@
         <v>282</v>
       </c>
       <c r="D88" s="37">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>171</v>
       </c>
       <c r="F88" s="36">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
@@ -3791,7 +3791,7 @@
         <v>213</v>
       </c>
       <c r="F109" s="36">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/levis.xlsx
+++ b/prix/levis.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\pages-GitHub Braconnier\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E34789-8F82-4DA8-9209-5A49BBCCBCC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49EBB961-2BF9-4FA5-9A17-1A63AD2003DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -995,7 +995,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="29">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1004,163 +1004,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.89999084444715716"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.749992370372631"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="-0.249977111117893"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1177,7 +1021,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1204,88 +1048,10 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1659,40 +1425,40 @@
       <c r="A2" t="s">
         <v>294</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="9" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D2" s="37">
-        <v>42</v>
+      <c r="D2" s="10">
+        <v>45</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="36">
-        <v>2</v>
+      <c r="F2" s="11">
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>294</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D3" s="37">
-        <v>42</v>
+      <c r="D3" s="10">
+        <v>45</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="36">
-        <v>6</v>
+      <c r="F3" s="11">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1705,14 +1471,14 @@
       <c r="C4" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D4" s="37">
+      <c r="D4" s="10">
         <v>94</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="36">
-        <v>4</v>
+      <c r="F4" s="11">
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1725,13 +1491,13 @@
       <c r="C5" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D5" s="37">
+      <c r="D5" s="10">
         <v>94</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="36">
+      <c r="F5" s="11">
         <v>5</v>
       </c>
     </row>
@@ -1739,19 +1505,19 @@
       <c r="A6" t="s">
         <v>294</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D6" s="37">
+      <c r="D6" s="10">
         <v>175</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="36">
+      <c r="F6" s="11">
         <v>6</v>
       </c>
     </row>
@@ -1759,19 +1525,19 @@
       <c r="A7" t="s">
         <v>294</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D7" s="37">
+      <c r="D7" s="10">
         <v>175</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="36">
+      <c r="F7" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1779,59 +1545,59 @@
       <c r="A8" t="s">
         <v>294</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="9" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D8" s="37">
+      <c r="D8" s="10">
         <v>175</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="36">
-        <v>6</v>
+      <c r="F8" s="11">
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>295</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="9" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D9" s="37">
+      <c r="D9" s="10">
         <v>47.25</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="36">
-        <v>2</v>
+      <c r="F9" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>296</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D10" s="37">
+      <c r="D10" s="10">
         <v>42</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="36">
+      <c r="F10" s="11">
         <v>2</v>
       </c>
     </row>
@@ -1839,19 +1605,19 @@
       <c r="A11" t="s">
         <v>296</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="9" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D11" s="37">
+      <c r="D11" s="10">
         <v>42</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="36">
+      <c r="F11" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1859,19 +1625,19 @@
       <c r="A12" t="s">
         <v>296</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D12" s="37">
+      <c r="D12" s="10">
         <v>42</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="36">
+      <c r="F12" s="11">
         <v>4</v>
       </c>
     </row>
@@ -1879,19 +1645,19 @@
       <c r="A13" t="s">
         <v>296</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="9" t="s">
         <v>23</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D13" s="37">
+      <c r="D13" s="10">
         <v>94</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="36">
+      <c r="F13" s="11">
         <v>2</v>
       </c>
     </row>
@@ -1899,19 +1665,19 @@
       <c r="A14" t="s">
         <v>296</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="9" t="s">
         <v>25</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D14" s="37">
+      <c r="D14" s="10">
         <v>94</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="36">
+      <c r="F14" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1919,19 +1685,19 @@
       <c r="A15" t="s">
         <v>296</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D15" s="37">
+      <c r="D15" s="10">
         <v>94</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="36">
+      <c r="F15" s="11">
         <v>3</v>
       </c>
     </row>
@@ -1939,19 +1705,19 @@
       <c r="A16" t="s">
         <v>296</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="9" t="s">
         <v>29</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D16" s="37">
+      <c r="D16" s="10">
         <v>175</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="36">
+      <c r="F16" s="11">
         <v>3</v>
       </c>
     </row>
@@ -1959,19 +1725,19 @@
       <c r="A17" t="s">
         <v>296</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D17" s="37">
+      <c r="D17" s="10">
         <v>175</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="36">
+      <c r="F17" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1979,36 +1745,36 @@
       <c r="A18" t="s">
         <v>296</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="9" t="s">
         <v>33</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D18" s="37">
+      <c r="D18" s="10">
         <v>175</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="36">
+      <c r="F18" s="11">
         <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="9" t="s">
         <v>35</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D19" s="37">
+      <c r="D19" s="10">
         <v>46.95</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F19" s="36">
+      <c r="F19" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2016,19 +1782,19 @@
       <c r="A20" t="s">
         <v>297</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="9" t="s">
         <v>37</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D20" s="37">
+      <c r="D20" s="10">
         <v>32</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F20" s="36">
+      <c r="F20" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2036,19 +1802,19 @@
       <c r="A21" t="s">
         <v>297</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="9" t="s">
         <v>39</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D21" s="37">
+      <c r="D21" s="10">
         <v>32</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F21" s="36">
+      <c r="F21" s="11">
         <v>3</v>
       </c>
     </row>
@@ -2056,19 +1822,19 @@
       <c r="A22" t="s">
         <v>297</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="9" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D22" s="37">
+      <c r="D22" s="10">
         <v>32</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F22" s="36">
+      <c r="F22" s="11">
         <v>3</v>
       </c>
     </row>
@@ -2076,19 +1842,19 @@
       <c r="A23" t="s">
         <v>297</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="9" t="s">
         <v>43</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D23" s="37">
+      <c r="D23" s="10">
         <v>58</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F23" s="36">
+      <c r="F23" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2096,19 +1862,19 @@
       <c r="A24" t="s">
         <v>297</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="9" t="s">
         <v>45</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D24" s="37">
+      <c r="D24" s="10">
         <v>58</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F24" s="36">
+      <c r="F24" s="11">
         <v>3</v>
       </c>
     </row>
@@ -2116,19 +1882,19 @@
       <c r="A25" t="s">
         <v>297</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="9" t="s">
         <v>47</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D25" s="37">
+      <c r="D25" s="10">
         <v>58</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F25" s="36">
+      <c r="F25" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2136,19 +1902,19 @@
       <c r="A26" t="s">
         <v>297</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="9" t="s">
         <v>49</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D26" s="37">
+      <c r="D26" s="10">
         <v>135.5</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F26" s="36">
+      <c r="F26" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2156,19 +1922,19 @@
       <c r="A27" t="s">
         <v>297</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D27" s="37">
+      <c r="D27" s="10">
         <v>135.5</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F27" s="36">
+      <c r="F27" s="11">
         <v>3</v>
       </c>
     </row>
@@ -2176,19 +1942,19 @@
       <c r="A28" t="s">
         <v>297</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="9" t="s">
         <v>53</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D28" s="37">
+      <c r="D28" s="10">
         <v>135.5</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="36">
+      <c r="F28" s="11">
         <v>7</v>
       </c>
     </row>
@@ -2196,39 +1962,39 @@
       <c r="A29" t="s">
         <v>293</v>
       </c>
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="9" t="s">
         <v>55</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D29" s="37">
+      <c r="D29" s="10">
         <v>36</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F29" s="36">
-        <v>5</v>
+      <c r="F29" s="11">
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>293</v>
       </c>
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="9" t="s">
         <v>57</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D30" s="37">
+      <c r="D30" s="10">
         <v>36</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="36">
+      <c r="F30" s="11">
         <v>6</v>
       </c>
     </row>
@@ -2236,19 +2002,19 @@
       <c r="A31" t="s">
         <v>293</v>
       </c>
-      <c r="B31" s="18" t="s">
+      <c r="B31" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D31" s="37">
+      <c r="D31" s="10">
         <v>37</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F31" s="36">
+      <c r="F31" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2256,39 +2022,39 @@
       <c r="A32" t="s">
         <v>293</v>
       </c>
-      <c r="B32" s="19" t="s">
+      <c r="B32" s="9" t="s">
         <v>61</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D32" s="37">
+      <c r="D32" s="10">
         <v>65</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F32" s="36">
-        <v>5</v>
+      <c r="F32" s="11">
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>293</v>
       </c>
-      <c r="B33" s="19" t="s">
+      <c r="B33" s="9" t="s">
         <v>63</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D33" s="37">
+      <c r="D33" s="10">
         <v>65</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F33" s="36">
+      <c r="F33" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2296,19 +2062,19 @@
       <c r="A34" t="s">
         <v>293</v>
       </c>
-      <c r="B34" s="19" t="s">
+      <c r="B34" s="9" t="s">
         <v>65</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D34" s="37">
+      <c r="D34" s="10">
         <v>65</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F34" s="36">
+      <c r="F34" s="11">
         <v>8</v>
       </c>
     </row>
@@ -2316,19 +2082,19 @@
       <c r="A35" t="s">
         <v>293</v>
       </c>
-      <c r="B35" s="20" t="s">
+      <c r="B35" s="9" t="s">
         <v>67</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D35" s="37">
+      <c r="D35" s="10">
         <v>150</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F35" s="36">
+      <c r="F35" s="11">
         <v>5</v>
       </c>
     </row>
@@ -2336,19 +2102,19 @@
       <c r="A36" t="s">
         <v>293</v>
       </c>
-      <c r="B36" s="20" t="s">
+      <c r="B36" s="9" t="s">
         <v>69</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D36" s="37">
+      <c r="D36" s="10">
         <v>150</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F36" s="36">
+      <c r="F36" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2356,39 +2122,39 @@
       <c r="A37" t="s">
         <v>293</v>
       </c>
-      <c r="B37" s="20" t="s">
+      <c r="B37" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D37" s="37">
+      <c r="D37" s="10">
         <v>150</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F37" s="36">
-        <v>2</v>
+      <c r="F37" s="11">
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>292</v>
       </c>
-      <c r="B38" s="21" t="s">
+      <c r="B38" s="9" t="s">
         <v>73</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D38" s="37">
+      <c r="D38" s="10">
         <v>36</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F38" s="36">
+      <c r="F38" s="11">
         <v>7</v>
       </c>
     </row>
@@ -2396,19 +2162,19 @@
       <c r="A39" t="s">
         <v>292</v>
       </c>
-      <c r="B39" s="21" t="s">
+      <c r="B39" s="9" t="s">
         <v>75</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D39" s="37">
+      <c r="D39" s="10">
         <v>36</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="36">
+      <c r="F39" s="11">
         <v>8</v>
       </c>
     </row>
@@ -2416,19 +2182,19 @@
       <c r="A40" t="s">
         <v>292</v>
       </c>
-      <c r="B40" s="21" t="s">
+      <c r="B40" s="9" t="s">
         <v>77</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D40" s="37">
+      <c r="D40" s="10">
         <v>36</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F40" s="36">
+      <c r="F40" s="11">
         <v>10</v>
       </c>
     </row>
@@ -2436,19 +2202,19 @@
       <c r="A41" t="s">
         <v>292</v>
       </c>
-      <c r="B41" s="22" t="s">
+      <c r="B41" s="9" t="s">
         <v>79</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D41" s="37">
+      <c r="D41" s="10">
         <v>65</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F41" s="36">
+      <c r="F41" s="11">
         <v>4</v>
       </c>
     </row>
@@ -2456,19 +2222,19 @@
       <c r="A42" t="s">
         <v>292</v>
       </c>
-      <c r="B42" s="22" t="s">
+      <c r="B42" s="9" t="s">
         <v>81</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D42" s="37">
+      <c r="D42" s="10">
         <v>65</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F42" s="36">
+      <c r="F42" s="11">
         <v>3</v>
       </c>
     </row>
@@ -2476,39 +2242,39 @@
       <c r="A43" t="s">
         <v>292</v>
       </c>
-      <c r="B43" s="22" t="s">
+      <c r="B43" s="9" t="s">
         <v>83</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D43" s="37">
+      <c r="D43" s="10">
         <v>65</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F43" s="36">
-        <v>4</v>
+      <c r="F43" s="11">
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>292</v>
       </c>
-      <c r="B44" s="23" t="s">
+      <c r="B44" s="9" t="s">
         <v>85</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D44" s="37">
+      <c r="D44" s="10">
         <v>145</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F44" s="36">
+      <c r="F44" s="11">
         <v>5</v>
       </c>
     </row>
@@ -2516,19 +2282,19 @@
       <c r="A45" t="s">
         <v>292</v>
       </c>
-      <c r="B45" s="23" t="s">
+      <c r="B45" s="9" t="s">
         <v>87</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D45" s="37">
+      <c r="D45" s="10">
         <v>145</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F45" s="36">
+      <c r="F45" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2536,19 +2302,19 @@
       <c r="A46" t="s">
         <v>292</v>
       </c>
-      <c r="B46" s="23" t="s">
+      <c r="B46" s="9" t="s">
         <v>89</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D46" s="37">
+      <c r="D46" s="10">
         <v>145</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F46" s="36">
+      <c r="F46" s="11">
         <v>3</v>
       </c>
     </row>
@@ -2556,199 +2322,199 @@
       <c r="A47" t="s">
         <v>301</v>
       </c>
-      <c r="B47" s="24" t="s">
+      <c r="B47" s="9" t="s">
         <v>91</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D47" s="37">
+      <c r="D47" s="10">
         <v>29.8</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F47" s="36">
-        <v>3</v>
+      <c r="F47" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>301</v>
       </c>
-      <c r="B48" s="24" t="s">
+      <c r="B48" s="9" t="s">
         <v>93</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D48" s="37">
+      <c r="D48" s="10">
         <v>29.8</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F48" s="36">
-        <v>4</v>
+      <c r="F48" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>301</v>
       </c>
-      <c r="B49" s="24" t="s">
+      <c r="B49" s="9" t="s">
         <v>95</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D49" s="37">
+      <c r="D49" s="10">
         <v>29.8</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F49" s="36">
-        <v>2</v>
+      <c r="F49" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>301</v>
       </c>
-      <c r="B50" s="25" t="s">
+      <c r="B50" s="9" t="s">
         <v>97</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D50" s="37">
+      <c r="D50" s="10">
         <v>69.150000000000006</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F50" s="36">
-        <v>1</v>
+      <c r="F50" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>301</v>
       </c>
-      <c r="B51" s="25" t="s">
+      <c r="B51" s="9" t="s">
         <v>99</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D51" s="37">
+      <c r="D51" s="10">
         <v>69.150000000000006</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F51" s="36">
-        <v>2</v>
+      <c r="F51" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>301</v>
       </c>
-      <c r="B52" s="25" t="s">
+      <c r="B52" s="9" t="s">
         <v>101</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D52" s="37">
+      <c r="D52" s="10">
         <v>69.150000000000006</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F52" s="36">
-        <v>3</v>
+      <c r="F52" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>301</v>
       </c>
-      <c r="B53" s="26" t="s">
+      <c r="B53" s="9" t="s">
         <v>103</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D53" s="37">
+      <c r="D53" s="10">
         <v>150.49</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F53" s="36">
-        <v>3</v>
+      <c r="F53" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>301</v>
       </c>
-      <c r="B54" s="26" t="s">
+      <c r="B54" s="9" t="s">
         <v>105</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D54" s="37">
+      <c r="D54" s="10">
         <v>150.49</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F54" s="36">
-        <v>2</v>
+      <c r="F54" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>301</v>
       </c>
-      <c r="B55" s="26" t="s">
+      <c r="B55" s="9" t="s">
         <v>107</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D55" s="37">
+      <c r="D55" s="10">
         <v>150.49</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="F55" s="36">
-        <v>0</v>
+      <c r="F55" s="11">
+        <v>-2</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>303</v>
       </c>
-      <c r="B56" s="27" t="s">
+      <c r="B56" s="9" t="s">
         <v>109</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D56" s="37">
+      <c r="D56" s="10">
         <v>35</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="F56" s="36">
+      <c r="F56" s="11">
         <v>5</v>
       </c>
     </row>
@@ -2756,19 +2522,19 @@
       <c r="A57" t="s">
         <v>303</v>
       </c>
-      <c r="B57" s="27" t="s">
+      <c r="B57" s="9" t="s">
         <v>111</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D57" s="37">
+      <c r="D57" s="10">
         <v>35</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="F57" s="36">
+      <c r="F57" s="11">
         <v>5</v>
       </c>
     </row>
@@ -2776,19 +2542,19 @@
       <c r="A58" t="s">
         <v>303</v>
       </c>
-      <c r="B58" s="27" t="s">
+      <c r="B58" s="9" t="s">
         <v>113</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D58" s="37">
+      <c r="D58" s="10">
         <v>35</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F58" s="36">
+      <c r="F58" s="11">
         <v>5</v>
       </c>
     </row>
@@ -2796,19 +2562,19 @@
       <c r="A59" t="s">
         <v>303</v>
       </c>
-      <c r="B59" s="28" t="s">
+      <c r="B59" s="9" t="s">
         <v>115</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D59" s="37">
+      <c r="D59" s="10">
         <v>151</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F59" s="36">
+      <c r="F59" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2816,19 +2582,19 @@
       <c r="A60" t="s">
         <v>303</v>
       </c>
-      <c r="B60" s="28" t="s">
+      <c r="B60" s="9" t="s">
         <v>117</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D60" s="37">
+      <c r="D60" s="10">
         <v>151</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F60" s="36">
+      <c r="F60" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2836,19 +2602,19 @@
       <c r="A61" t="s">
         <v>303</v>
       </c>
-      <c r="B61" s="28" t="s">
+      <c r="B61" s="9" t="s">
         <v>119</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D61" s="37">
+      <c r="D61" s="10">
         <v>151</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F61" s="36">
+      <c r="F61" s="11">
         <v>4</v>
       </c>
     </row>
@@ -2856,19 +2622,19 @@
       <c r="A62" t="s">
         <v>304</v>
       </c>
-      <c r="B62" s="29" t="s">
+      <c r="B62" s="9" t="s">
         <v>121</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D62" s="37">
+      <c r="D62" s="10">
         <v>37</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F62" s="36">
+      <c r="F62" s="11">
         <v>5</v>
       </c>
     </row>
@@ -2876,19 +2642,19 @@
       <c r="A63" t="s">
         <v>304</v>
       </c>
-      <c r="B63" s="29" t="s">
+      <c r="B63" s="9" t="s">
         <v>123</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D63" s="37">
+      <c r="D63" s="10">
         <v>37</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="F63" s="36">
+      <c r="F63" s="11">
         <v>6</v>
       </c>
     </row>
@@ -2896,19 +2662,19 @@
       <c r="A64" t="s">
         <v>304</v>
       </c>
-      <c r="B64" s="29" t="s">
+      <c r="B64" s="9" t="s">
         <v>125</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D64" s="37">
+      <c r="D64" s="10">
         <v>37</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="F64" s="36">
+      <c r="F64" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2916,19 +2682,19 @@
       <c r="A65" t="s">
         <v>304</v>
       </c>
-      <c r="B65" s="19" t="s">
+      <c r="B65" s="9" t="s">
         <v>127</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D65" s="37">
+      <c r="D65" s="10">
         <v>42.300000000000004</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="F65" s="36">
+      <c r="F65" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2936,19 +2702,19 @@
       <c r="A66" t="s">
         <v>304</v>
       </c>
-      <c r="B66" s="19" t="s">
+      <c r="B66" s="9" t="s">
         <v>129</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D66" s="37">
+      <c r="D66" s="10">
         <v>42.300000000000004</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="F66" s="36">
+      <c r="F66" s="11">
         <v>3</v>
       </c>
     </row>
@@ -2956,19 +2722,19 @@
       <c r="A67" t="s">
         <v>304</v>
       </c>
-      <c r="B67" s="19" t="s">
+      <c r="B67" s="9" t="s">
         <v>131</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D67" s="37">
+      <c r="D67" s="10">
         <v>42.300000000000004</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="F67" s="36">
+      <c r="F67" s="11">
         <v>3</v>
       </c>
     </row>
@@ -2976,19 +2742,19 @@
       <c r="A68" t="s">
         <v>304</v>
       </c>
-      <c r="B68" s="20" t="s">
+      <c r="B68" s="9" t="s">
         <v>133</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D68" s="37">
+      <c r="D68" s="10">
         <v>109.49000000000001</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="F68" s="36">
+      <c r="F68" s="11">
         <v>1</v>
       </c>
     </row>
@@ -2996,19 +2762,19 @@
       <c r="A69" t="s">
         <v>304</v>
       </c>
-      <c r="B69" s="20" t="s">
+      <c r="B69" s="9" t="s">
         <v>135</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D69" s="37">
+      <c r="D69" s="10">
         <v>96.850000000000009</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="F69" s="36">
+      <c r="F69" s="11">
         <v>2</v>
       </c>
     </row>
@@ -3016,19 +2782,19 @@
       <c r="A70" t="s">
         <v>304</v>
       </c>
-      <c r="B70" s="20" t="s">
+      <c r="B70" s="9" t="s">
         <v>137</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D70" s="37">
+      <c r="D70" s="10">
         <v>96.850000000000009</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="F70" s="36">
+      <c r="F70" s="11">
         <v>2</v>
       </c>
     </row>
@@ -3036,19 +2802,19 @@
       <c r="A71" t="s">
         <v>305</v>
       </c>
-      <c r="B71" s="30" t="s">
+      <c r="B71" s="9" t="s">
         <v>139</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D71" s="37">
+      <c r="D71" s="10">
         <v>37</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="F71" s="36">
+      <c r="F71" s="11">
         <v>0</v>
       </c>
     </row>
@@ -3056,19 +2822,19 @@
       <c r="A72" t="s">
         <v>305</v>
       </c>
-      <c r="B72" s="30" t="s">
+      <c r="B72" s="9" t="s">
         <v>141</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D72" s="37">
+      <c r="D72" s="10">
         <v>34</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="F72" s="36">
+      <c r="F72" s="11">
         <v>1</v>
       </c>
     </row>
@@ -3076,19 +2842,19 @@
       <c r="A73" t="s">
         <v>305</v>
       </c>
-      <c r="B73" s="30" t="s">
+      <c r="B73" s="9" t="s">
         <v>143</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D73" s="37">
+      <c r="D73" s="10">
         <v>34</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="F73" s="36">
+      <c r="F73" s="11">
         <v>4</v>
       </c>
     </row>
@@ -3096,19 +2862,19 @@
       <c r="A74" t="s">
         <v>305</v>
       </c>
-      <c r="B74" s="31" t="s">
+      <c r="B74" s="9" t="s">
         <v>145</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D74" s="37">
+      <c r="D74" s="10">
         <v>46.5</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F74" s="36">
+      <c r="F74" s="11">
         <v>2</v>
       </c>
     </row>
@@ -3116,19 +2882,19 @@
       <c r="A75" t="s">
         <v>305</v>
       </c>
-      <c r="B75" s="31" t="s">
+      <c r="B75" s="9" t="s">
         <v>147</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D75" s="37">
+      <c r="D75" s="10">
         <v>60</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="F75" s="36">
+      <c r="F75" s="11">
         <v>1</v>
       </c>
     </row>
@@ -3136,19 +2902,19 @@
       <c r="A76" t="s">
         <v>305</v>
       </c>
-      <c r="B76" s="31" t="s">
+      <c r="B76" s="9" t="s">
         <v>149</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D76" s="37">
+      <c r="D76" s="10">
         <v>60</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="F76" s="36">
+      <c r="F76" s="11">
         <v>7</v>
       </c>
     </row>
@@ -3156,19 +2922,19 @@
       <c r="A77" t="s">
         <v>305</v>
       </c>
-      <c r="B77" s="32" t="s">
+      <c r="B77" s="9" t="s">
         <v>151</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D77" s="37">
+      <c r="D77" s="10">
         <v>136</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="F77" s="36">
+      <c r="F77" s="11">
         <v>2</v>
       </c>
     </row>
@@ -3176,19 +2942,19 @@
       <c r="A78" t="s">
         <v>305</v>
       </c>
-      <c r="B78" s="32" t="s">
+      <c r="B78" s="9" t="s">
         <v>153</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D78" s="37">
+      <c r="D78" s="10">
         <v>136</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F78" s="36">
+      <c r="F78" s="11">
         <v>2</v>
       </c>
     </row>
@@ -3196,19 +2962,19 @@
       <c r="A79" t="s">
         <v>305</v>
       </c>
-      <c r="B79" s="32" t="s">
+      <c r="B79" s="9" t="s">
         <v>155</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D79" s="37">
+      <c r="D79" s="10">
         <v>136</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="F79" s="36">
+      <c r="F79" s="11">
         <v>0</v>
       </c>
     </row>
@@ -3216,19 +2982,19 @@
       <c r="A80" t="s">
         <v>300</v>
       </c>
-      <c r="B80" s="15" t="s">
+      <c r="B80" s="9" t="s">
         <v>157</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D80" s="37">
+      <c r="D80" s="10">
         <v>53</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="F80" s="36">
+      <c r="F80" s="11">
         <v>4</v>
       </c>
     </row>
@@ -3236,19 +3002,19 @@
       <c r="A81" t="s">
         <v>300</v>
       </c>
-      <c r="B81" s="15" t="s">
+      <c r="B81" s="9" t="s">
         <v>159</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D81" s="37">
+      <c r="D81" s="10">
         <v>53</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="F81" s="36">
+      <c r="F81" s="11">
         <v>1</v>
       </c>
     </row>
@@ -3256,19 +3022,19 @@
       <c r="A82" t="s">
         <v>300</v>
       </c>
-      <c r="B82" s="16" t="s">
+      <c r="B82" s="9" t="s">
         <v>161</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D82" s="37">
+      <c r="D82" s="10">
         <v>123</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="F82" s="36">
+      <c r="F82" s="11">
         <v>3</v>
       </c>
     </row>
@@ -3276,53 +3042,53 @@
       <c r="A83" t="s">
         <v>300</v>
       </c>
-      <c r="B83" s="16" t="s">
+      <c r="B83" s="9" t="s">
         <v>163</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D83" s="37">
+      <c r="D83" s="10">
         <v>123</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="F83" s="36">
+      <c r="F83" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B84" s="2" t="s">
+      <c r="B84" s="9" t="s">
         <v>165</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="D84" s="37">
+      <c r="D84" s="10">
         <v>36</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="F84" s="36">
+      <c r="F84" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B85" s="2" t="s">
+      <c r="B85" s="9" t="s">
         <v>165</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D85" s="37">
+      <c r="D85" s="10">
         <v>107</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="F85" s="36">
+      <c r="F85" s="11">
         <v>3</v>
       </c>
     </row>
@@ -3330,19 +3096,19 @@
       <c r="A86" t="s">
         <v>299</v>
       </c>
-      <c r="B86" s="26" t="s">
+      <c r="B86" s="9" t="s">
         <v>168</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D86" s="37">
+      <c r="D86" s="10">
         <v>39.5</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="F86" s="36">
+      <c r="F86" s="11">
         <v>2</v>
       </c>
     </row>
@@ -3350,19 +3116,19 @@
       <c r="A87" t="s">
         <v>299</v>
       </c>
-      <c r="B87" s="26" t="s">
+      <c r="B87" s="9" t="s">
         <v>170</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D87" s="37">
+      <c r="D87" s="10">
         <v>39.5</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="F87" s="36">
+      <c r="F87" s="11">
         <v>2</v>
       </c>
     </row>
@@ -3370,19 +3136,19 @@
       <c r="A88" t="s">
         <v>299</v>
       </c>
-      <c r="B88" s="27" t="s">
+      <c r="B88" s="9" t="s">
         <v>172</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D88" s="37">
+      <c r="D88" s="10">
         <v>90</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="F88" s="36">
+      <c r="F88" s="11">
         <v>2</v>
       </c>
     </row>
@@ -3390,19 +3156,19 @@
       <c r="A89" t="s">
         <v>299</v>
       </c>
-      <c r="B89" s="27" t="s">
+      <c r="B89" s="9" t="s">
         <v>174</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D89" s="37">
+      <c r="D89" s="10">
         <v>86</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="F89" s="36">
+      <c r="F89" s="11">
         <v>3</v>
       </c>
     </row>
@@ -3410,19 +3176,19 @@
       <c r="A90" t="s">
         <v>299</v>
       </c>
-      <c r="B90" s="28" t="s">
+      <c r="B90" s="9" t="s">
         <v>176</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D90" s="37">
+      <c r="D90" s="10">
         <v>130</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="F90" s="36">
+      <c r="F90" s="11">
         <v>1</v>
       </c>
     </row>
@@ -3430,90 +3196,90 @@
       <c r="A91" t="s">
         <v>299</v>
       </c>
-      <c r="B91" s="28" t="s">
+      <c r="B91" s="9" t="s">
         <v>178</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D91" s="37">
+      <c r="D91" s="10">
         <v>130</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="F91" s="36">
+      <c r="F91" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B92" s="2" t="s">
+      <c r="B92" s="9" t="s">
         <v>180</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D92" s="37">
+      <c r="D92" s="10">
         <v>34.5</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="F92" s="36">
+      <c r="F92" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B93" s="2" t="s">
+      <c r="B93" s="9" t="s">
         <v>182</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D93" s="37">
+      <c r="D93" s="10">
         <v>71.5</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F93" s="36">
+      <c r="F93" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B94" s="2" t="s">
+      <c r="B94" s="9" t="s">
         <v>184</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="D94" s="37">
+      <c r="D94" s="10">
         <v>131.5</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="F94" s="36">
-        <v>1</v>
+      <c r="F94" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>298</v>
       </c>
-      <c r="B95" s="21" t="s">
+      <c r="B95" s="9" t="s">
         <v>186</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D95" s="37">
+      <c r="D95" s="10">
         <v>36</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="F95" s="36">
+      <c r="F95" s="11">
         <v>3</v>
       </c>
     </row>
@@ -3521,19 +3287,19 @@
       <c r="A96" t="s">
         <v>298</v>
       </c>
-      <c r="B96" s="21" t="s">
+      <c r="B96" s="9" t="s">
         <v>188</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D96" s="37">
+      <c r="D96" s="10">
         <v>36</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="F96" s="36">
+      <c r="F96" s="11">
         <v>2</v>
       </c>
     </row>
@@ -3541,19 +3307,19 @@
       <c r="A97" t="s">
         <v>298</v>
       </c>
-      <c r="B97" s="22" t="s">
+      <c r="B97" s="9" t="s">
         <v>190</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D97" s="37">
+      <c r="D97" s="10">
         <v>78</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="F97" s="36">
+      <c r="F97" s="11">
         <v>3</v>
       </c>
     </row>
@@ -3561,19 +3327,19 @@
       <c r="A98" t="s">
         <v>298</v>
       </c>
-      <c r="B98" s="22" t="s">
+      <c r="B98" s="9" t="s">
         <v>192</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D98" s="37">
+      <c r="D98" s="10">
         <v>78</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="F98" s="36">
+      <c r="F98" s="11">
         <v>2</v>
       </c>
     </row>
@@ -3581,19 +3347,19 @@
       <c r="A99" t="s">
         <v>298</v>
       </c>
-      <c r="B99" s="23" t="s">
+      <c r="B99" s="9" t="s">
         <v>194</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D99" s="37">
+      <c r="D99" s="10">
         <v>145</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="F99" s="36">
+      <c r="F99" s="11">
         <v>2</v>
       </c>
     </row>
@@ -3601,36 +3367,36 @@
       <c r="A100" t="s">
         <v>298</v>
       </c>
-      <c r="B100" s="23" t="s">
+      <c r="B100" s="9" t="s">
         <v>196</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D100" s="37">
+      <c r="D100" s="10">
         <v>145</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="F100" s="36">
+      <c r="F100" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B101" s="2" t="s">
+      <c r="B101" s="9" t="s">
         <v>198</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D101" s="37">
+      <c r="D101" s="10">
         <v>55</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="F101" s="36">
+      <c r="F101" s="11">
         <v>0</v>
       </c>
     </row>
@@ -3638,39 +3404,39 @@
       <c r="A102" t="s">
         <v>306</v>
       </c>
-      <c r="B102" s="2" t="s">
+      <c r="B102" s="9" t="s">
         <v>200</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D102" s="37">
+      <c r="D102" s="10">
         <v>35.5</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="F102" s="36">
-        <v>4</v>
+      <c r="F102" s="11">
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>306</v>
       </c>
-      <c r="B103" s="30" t="s">
+      <c r="B103" s="9" t="s">
         <v>202</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D103" s="37">
+      <c r="D103" s="10">
         <v>35.5</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="F103" s="36">
+      <c r="F103" s="11">
         <v>0</v>
       </c>
     </row>
@@ -3678,19 +3444,19 @@
       <c r="A104" t="s">
         <v>306</v>
       </c>
-      <c r="B104" s="30" t="s">
+      <c r="B104" s="9" t="s">
         <v>204</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D104" s="37">
+      <c r="D104" s="10">
         <v>35.5</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="F104" s="36">
+      <c r="F104" s="11">
         <v>4</v>
       </c>
     </row>
@@ -3698,19 +3464,19 @@
       <c r="A105" t="s">
         <v>306</v>
       </c>
-      <c r="B105" s="31" t="s">
+      <c r="B105" s="9" t="s">
         <v>206</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D105" s="37">
+      <c r="D105" s="10">
         <v>53.95</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="F105" s="36">
+      <c r="F105" s="11">
         <v>0</v>
       </c>
     </row>
@@ -3718,39 +3484,39 @@
       <c r="A106" t="s">
         <v>306</v>
       </c>
-      <c r="B106" s="31" t="s">
+      <c r="B106" s="9" t="s">
         <v>208</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D106" s="37">
+      <c r="D106" s="10">
         <v>59</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="F106" s="36">
-        <v>6</v>
+      <c r="F106" s="11">
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>306</v>
       </c>
-      <c r="B107" s="31" t="s">
+      <c r="B107" s="9" t="s">
         <v>210</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D107" s="37">
+      <c r="D107" s="10">
         <v>53.95</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F107" s="36">
+      <c r="F107" s="11">
         <v>4</v>
       </c>
     </row>
@@ -3758,19 +3524,19 @@
       <c r="A108" t="s">
         <v>306</v>
       </c>
-      <c r="B108" s="32" t="s">
+      <c r="B108" s="9" t="s">
         <v>212</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D108" s="37">
+      <c r="D108" s="10">
         <v>146</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="F108" s="36">
+      <c r="F108" s="11">
         <v>0</v>
       </c>
     </row>
@@ -3778,19 +3544,19 @@
       <c r="A109" t="s">
         <v>306</v>
       </c>
-      <c r="B109" s="32" t="s">
+      <c r="B109" s="9" t="s">
         <v>214</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D109" s="37">
+      <c r="D109" s="10">
         <v>146</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="F109" s="36">
+      <c r="F109" s="11">
         <v>3</v>
       </c>
     </row>
@@ -3798,19 +3564,19 @@
       <c r="A110" t="s">
         <v>306</v>
       </c>
-      <c r="B110" s="32" t="s">
+      <c r="B110" s="9" t="s">
         <v>216</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D110" s="37">
+      <c r="D110" s="10">
         <v>146</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="F110" s="36">
+      <c r="F110" s="11">
         <v>2</v>
       </c>
     </row>
@@ -3818,19 +3584,19 @@
       <c r="A111" t="s">
         <v>307</v>
       </c>
-      <c r="B111" s="33" t="s">
+      <c r="B111" s="9" t="s">
         <v>218</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D111" s="37">
+      <c r="D111" s="10">
         <v>20.5</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="F111" s="36">
+      <c r="F111" s="11">
         <v>4</v>
       </c>
     </row>
@@ -3838,19 +3604,19 @@
       <c r="A112" t="s">
         <v>307</v>
       </c>
-      <c r="B112" s="11" t="s">
+      <c r="B112" s="9" t="s">
         <v>220</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D112" s="37">
+      <c r="D112" s="10">
         <v>34.15</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="F112" s="36">
+      <c r="F112" s="11">
         <v>1</v>
       </c>
     </row>
@@ -3858,19 +3624,19 @@
       <c r="A113" t="s">
         <v>307</v>
       </c>
-      <c r="B113" s="11" t="s">
+      <c r="B113" s="9" t="s">
         <v>222</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D113" s="37">
+      <c r="D113" s="10">
         <v>34.15</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="F113" s="36">
+      <c r="F113" s="11">
         <v>1</v>
       </c>
     </row>
@@ -3878,104 +3644,104 @@
       <c r="A114" t="s">
         <v>307</v>
       </c>
-      <c r="B114" s="12" t="s">
+      <c r="B114" s="9" t="s">
         <v>224</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D114" s="37">
+      <c r="D114" s="10">
         <v>76.350000000000009</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="F114" s="36">
+      <c r="F114" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B115" s="2" t="s">
+      <c r="B115" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="D115" s="37">
+      <c r="D115" s="10">
         <v>6.55</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F115" s="36">
+      <c r="F115" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B116" s="2" t="s">
+      <c r="B116" s="9" t="s">
         <v>228</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D116" s="37">
+      <c r="D116" s="10">
         <v>8.5</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="F116" s="36">
+      <c r="F116" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B117" s="2" t="s">
+      <c r="B117" s="9" t="s">
         <v>230</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D117" s="37">
+      <c r="D117" s="10">
         <v>8.5</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F117" s="36">
+      <c r="F117" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B118" s="2" t="s">
+      <c r="B118" s="9" t="s">
         <v>232</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D118" s="37">
+      <c r="D118" s="10">
         <v>8.5</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="F118" s="36">
-        <v>6</v>
+      <c r="F118" s="11">
+        <v>2</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>308</v>
       </c>
-      <c r="B119" s="21" t="s">
+      <c r="B119" s="9" t="s">
         <v>234</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D119" s="37">
+      <c r="D119" s="10">
         <v>46.35</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="F119" s="36">
+      <c r="F119" s="11">
         <v>3</v>
       </c>
     </row>
@@ -3983,19 +3749,19 @@
       <c r="A120" t="s">
         <v>308</v>
       </c>
-      <c r="B120" s="21" t="s">
+      <c r="B120" s="9" t="s">
         <v>236</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D120" s="37">
+      <c r="D120" s="10">
         <v>46.35</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="F120" s="36">
+      <c r="F120" s="11">
         <v>2</v>
       </c>
     </row>
@@ -4003,19 +3769,19 @@
       <c r="A121" t="s">
         <v>308</v>
       </c>
-      <c r="B121" s="22" t="s">
+      <c r="B121" s="9" t="s">
         <v>238</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D121" s="37">
+      <c r="D121" s="10">
         <v>107.35000000000001</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F121" s="36">
+      <c r="F121" s="11">
         <v>2</v>
       </c>
     </row>
@@ -4023,39 +3789,39 @@
       <c r="A122" t="s">
         <v>302</v>
       </c>
-      <c r="B122" s="29" t="s">
+      <c r="B122" s="9" t="s">
         <v>240</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D122" s="37">
+      <c r="D122" s="10">
         <v>52</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="F122" s="36">
-        <v>4</v>
+      <c r="F122" s="11">
+        <v>3</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>302</v>
       </c>
-      <c r="B123" s="29" t="s">
+      <c r="B123" s="9" t="s">
         <v>242</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D123" s="37">
+      <c r="D123" s="10">
         <v>52</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="F123" s="36">
+      <c r="F123" s="11">
         <v>0</v>
       </c>
     </row>
@@ -4063,19 +3829,19 @@
       <c r="A124" t="s">
         <v>302</v>
       </c>
-      <c r="B124" s="29" t="s">
+      <c r="B124" s="9" t="s">
         <v>244</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D124" s="37">
+      <c r="D124" s="10">
         <v>52</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="F124" s="36">
+      <c r="F124" s="11">
         <v>2</v>
       </c>
     </row>
@@ -4083,19 +3849,19 @@
       <c r="A125" t="s">
         <v>302</v>
       </c>
-      <c r="B125" s="34" t="s">
+      <c r="B125" s="9" t="s">
         <v>246</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D125" s="37">
+      <c r="D125" s="10">
         <v>95.990000000000009</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="F125" s="36">
+      <c r="F125" s="11">
         <v>3</v>
       </c>
     </row>
@@ -4103,19 +3869,19 @@
       <c r="A126" t="s">
         <v>302</v>
       </c>
-      <c r="B126" s="34" t="s">
+      <c r="B126" s="9" t="s">
         <v>248</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D126" s="37">
+      <c r="D126" s="10">
         <v>114.49000000000001</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="F126" s="36">
+      <c r="F126" s="11">
         <v>2</v>
       </c>
     </row>
@@ -4123,19 +3889,19 @@
       <c r="A127" t="s">
         <v>302</v>
       </c>
-      <c r="B127" s="34" t="s">
+      <c r="B127" s="9" t="s">
         <v>250</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D127" s="37">
+      <c r="D127" s="10">
         <v>95.990000000000009</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="F127" s="36">
+      <c r="F127" s="11">
         <v>1</v>
       </c>
     </row>
@@ -4143,19 +3909,19 @@
       <c r="A128" t="s">
         <v>302</v>
       </c>
-      <c r="B128" s="35" t="s">
+      <c r="B128" s="9" t="s">
         <v>252</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D128" s="37">
+      <c r="D128" s="10">
         <v>212</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="F128" s="36">
+      <c r="F128" s="11">
         <v>2</v>
       </c>
     </row>
@@ -4163,19 +3929,19 @@
       <c r="A129" t="s">
         <v>302</v>
       </c>
-      <c r="B129" s="35" t="s">
+      <c r="B129" s="9" t="s">
         <v>254</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D129" s="37">
+      <c r="D129" s="10">
         <v>212</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="F129" s="36">
+      <c r="F129" s="11">
         <v>4</v>
       </c>
     </row>
@@ -4183,155 +3949,155 @@
       <c r="A130" t="s">
         <v>302</v>
       </c>
-      <c r="B130" s="35" t="s">
+      <c r="B130" s="9" t="s">
         <v>256</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D130" s="37">
+      <c r="D130" s="10">
         <v>212</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="F130" s="36">
+      <c r="F130" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B131" s="2" t="s">
+      <c r="B131" s="9" t="s">
         <v>258</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D131" s="37">
+      <c r="D131" s="10">
         <v>63.4</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="F131" s="36">
+      <c r="F131" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B132" s="2" t="s">
+      <c r="B132" s="9" t="s">
         <v>260</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="D132" s="37">
+      <c r="D132" s="10">
         <v>40</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="F132" s="36">
+      <c r="F132" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B133" s="2" t="s">
+      <c r="B133" s="9" t="s">
         <v>262</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D133" s="37">
+      <c r="D133" s="10">
         <v>71.989999999999995</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="F133" s="36">
+      <c r="F133" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B134" s="2" t="s">
+      <c r="B134" s="9" t="s">
         <v>264</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D134" s="37">
+      <c r="D134" s="10">
         <v>108.31</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F134" s="36">
+      <c r="F134" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B135" s="2" t="s">
+      <c r="B135" s="9" t="s">
         <v>266</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D135" s="37">
+      <c r="D135" s="10">
         <v>73.650000000000006</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="F135" s="36">
+      <c r="F135" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B136" s="2" t="s">
+      <c r="B136" s="9" t="s">
         <v>268</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D136" s="37">
+      <c r="D136" s="10">
         <v>73.650000000000006</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="F136" s="36">
+      <c r="F136" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B137" s="2" t="s">
+      <c r="B137" s="9" t="s">
         <v>270</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="D137" s="37">
+      <c r="D137" s="10">
         <v>190</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="F137" s="36">
+      <c r="F137" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B138" s="2" t="s">
+      <c r="B138" s="9" t="s">
         <v>272</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D138" s="37">
+      <c r="D138" s="10">
         <v>67</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="F138" s="36">
+      <c r="F138" s="11">
         <v>1</v>
       </c>
     </row>

--- a/prix/levis.xlsx
+++ b/prix/levis.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\pages-GitHub Braconnier\peintures\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49EBB961-2BF9-4FA5-9A17-1A63AD2003DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B7C67DC-F16B-4A12-AA15-5FF52FF0E67C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="305">
   <si>
     <t>31100072</t>
   </si>
@@ -809,12 +809,6 @@
     <t>Facade expert (BASE M)-5l</t>
   </si>
   <si>
-    <t>31101022</t>
-  </si>
-  <si>
-    <t>Ambiance plafond extra mat 0001 2.5</t>
-  </si>
-  <si>
     <t>31101056</t>
   </si>
   <si>
@@ -831,12 +825,6 @@
   </si>
   <si>
     <t>Levis expert façade blanc 2.5lt</t>
-  </si>
-  <si>
-    <t>31101066</t>
-  </si>
-  <si>
-    <t>Levis expert façade naturel 2.5lt</t>
   </si>
   <si>
     <t>31101068</t>
@@ -1021,7 +1009,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1047,6 +1035,12 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1388,7 +1382,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{065E4AF0-A4F8-4CE3-9E23-EDCEACB756BD}">
-  <dimension ref="A1:G446"/>
+  <dimension ref="A1:G444"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
@@ -1402,3366 +1396,3639 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="F1" s="8" t="s">
         <v>274</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>278</v>
       </c>
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D2" s="10">
+        <v>275</v>
+      </c>
+      <c r="D2" s="12">
         <v>45</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="13">
         <v>7</v>
       </c>
+      <c r="G2" s="11"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D3" s="10">
+        <v>275</v>
+      </c>
+      <c r="D3" s="12">
         <v>45</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="11">
-        <v>2</v>
-      </c>
+      <c r="F3" s="13">
+        <v>8</v>
+      </c>
+      <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D4" s="10">
+        <v>278</v>
+      </c>
+      <c r="D4" s="12">
         <v>94</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="13">
         <v>6</v>
       </c>
+      <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D5" s="10">
+        <v>278</v>
+      </c>
+      <c r="D5" s="12">
         <v>94</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="11">
-        <v>5</v>
-      </c>
+      <c r="F5" s="13">
+        <v>4</v>
+      </c>
+      <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D6" s="10">
+        <v>277</v>
+      </c>
+      <c r="D6" s="12">
         <v>175</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="13">
         <v>6</v>
       </c>
+      <c r="G6" s="11"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D7" s="10">
+        <v>277</v>
+      </c>
+      <c r="D7" s="12">
         <v>175</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="13">
         <v>1</v>
       </c>
+      <c r="G7" s="11"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D8" s="10">
+        <v>277</v>
+      </c>
+      <c r="D8" s="12">
         <v>175</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="11">
-        <v>5</v>
-      </c>
+      <c r="F8" s="13">
+        <v>4</v>
+      </c>
+      <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D9" s="10">
+        <v>275</v>
+      </c>
+      <c r="D9" s="12">
         <v>47.25</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="13">
         <v>0</v>
       </c>
+      <c r="G9" s="11"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D10" s="10">
-        <v>42</v>
+        <v>275</v>
+      </c>
+      <c r="D10" s="12">
+        <v>45</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="11">
-        <v>2</v>
-      </c>
+      <c r="F10" s="13">
+        <v>4</v>
+      </c>
+      <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D11" s="10">
-        <v>42</v>
+        <v>275</v>
+      </c>
+      <c r="D11" s="12">
+        <v>45</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="13">
         <v>0</v>
       </c>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D12" s="10">
-        <v>42</v>
+        <v>275</v>
+      </c>
+      <c r="D12" s="12">
+        <v>45</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="13">
         <v>4</v>
       </c>
+      <c r="G12" s="11"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>23</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D13" s="10">
+        <v>278</v>
+      </c>
+      <c r="D13" s="12">
         <v>94</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="13">
         <v>2</v>
       </c>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>25</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D14" s="10">
+        <v>278</v>
+      </c>
+      <c r="D14" s="12">
         <v>94</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="13">
         <v>0</v>
       </c>
+      <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D15" s="10">
+        <v>278</v>
+      </c>
+      <c r="D15" s="12">
         <v>94</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="11">
-        <v>3</v>
-      </c>
+      <c r="F15" s="13">
+        <v>2</v>
+      </c>
+      <c r="G15" s="11"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>29</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D16" s="10">
+        <v>277</v>
+      </c>
+      <c r="D16" s="12">
         <v>175</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G16" s="11"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D17" s="10">
+        <v>277</v>
+      </c>
+      <c r="D17" s="12">
         <v>175</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G17" s="11"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>33</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D18" s="10">
+        <v>277</v>
+      </c>
+      <c r="D18" s="12">
         <v>175</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="13">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G18" s="11"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B19" s="9" t="s">
         <v>35</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D19" s="10">
+        <v>275</v>
+      </c>
+      <c r="D19" s="12">
         <v>46.95</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G19" s="11"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>37</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D20" s="10">
+        <v>279</v>
+      </c>
+      <c r="D20" s="12">
         <v>32</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F20" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F20" s="13">
+        <v>1</v>
+      </c>
+      <c r="G20" s="11"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>39</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D21" s="10">
+        <v>279</v>
+      </c>
+      <c r="D21" s="12">
         <v>32</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F21" s="11">
+      <c r="F21" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G21" s="11"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D22" s="10">
+        <v>279</v>
+      </c>
+      <c r="D22" s="12">
         <v>32</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G22" s="11"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>43</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D23" s="10">
+        <v>275</v>
+      </c>
+      <c r="D23" s="12">
         <v>58</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F23" s="11">
+      <c r="F23" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G23" s="11"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>45</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D24" s="10">
+        <v>275</v>
+      </c>
+      <c r="D24" s="12">
         <v>58</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F24" s="11">
+      <c r="F24" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G24" s="11"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>47</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D25" s="10">
+        <v>275</v>
+      </c>
+      <c r="D25" s="12">
         <v>58</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F25" s="11">
+      <c r="F25" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G25" s="11"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>49</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D26" s="10">
+        <v>278</v>
+      </c>
+      <c r="D26" s="12">
         <v>135.5</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F26" s="11">
+      <c r="F26" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G26" s="11"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D27" s="10">
+        <v>278</v>
+      </c>
+      <c r="D27" s="12">
         <v>135.5</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F27" s="11">
+      <c r="F27" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G27" s="11"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>53</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D28" s="10">
+        <v>278</v>
+      </c>
+      <c r="D28" s="12">
         <v>135.5</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="11">
+      <c r="F28" s="13">
         <v>7</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G28" s="11"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>55</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D29" s="10">
+        <v>279</v>
+      </c>
+      <c r="D29" s="12">
         <v>36</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F29" s="11">
+      <c r="F29" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G29" s="11"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>57</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D30" s="10">
+        <v>279</v>
+      </c>
+      <c r="D30" s="12">
         <v>36</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="11">
+      <c r="F30" s="13">
         <v>6</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G30" s="11"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D31" s="10">
+        <v>279</v>
+      </c>
+      <c r="D31" s="12">
         <v>37</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F31" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F31" s="13">
+        <v>8</v>
+      </c>
+      <c r="G31" s="11"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>61</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D32" s="10">
+        <v>275</v>
+      </c>
+      <c r="D32" s="12">
         <v>65</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F32" s="11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F32" s="13">
+        <v>3</v>
+      </c>
+      <c r="G32" s="11"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>63</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D33" s="10">
+        <v>275</v>
+      </c>
+      <c r="D33" s="12">
         <v>65</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F33" s="11">
+      <c r="F33" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G33" s="11"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>65</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D34" s="10">
+        <v>275</v>
+      </c>
+      <c r="D34" s="12">
         <v>65</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F34" s="11">
+      <c r="F34" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G34" s="11"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>67</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D35" s="10">
+        <v>278</v>
+      </c>
+      <c r="D35" s="12">
         <v>150</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F35" s="11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F35" s="13">
+        <v>6</v>
+      </c>
+      <c r="G35" s="11"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>69</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D36" s="10">
+        <v>278</v>
+      </c>
+      <c r="D36" s="12">
         <v>150</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F36" s="11">
+      <c r="F36" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G36" s="11"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D37" s="10">
+        <v>278</v>
+      </c>
+      <c r="D37" s="12">
         <v>150</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F37" s="11">
+      <c r="F37" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G37" s="11"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>73</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D38" s="10">
+        <v>279</v>
+      </c>
+      <c r="D38" s="12">
         <v>36</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F38" s="11">
+      <c r="F38" s="13">
         <v>7</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G38" s="11"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B39" s="9" t="s">
         <v>75</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D39" s="10">
+        <v>279</v>
+      </c>
+      <c r="D39" s="12">
         <v>36</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="11">
+      <c r="F39" s="13">
         <v>8</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G39" s="11"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B40" s="9" t="s">
         <v>77</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D40" s="10">
+        <v>279</v>
+      </c>
+      <c r="D40" s="12">
         <v>36</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F40" s="11">
+      <c r="F40" s="13">
         <v>10</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G40" s="11"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>79</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D41" s="10">
+        <v>275</v>
+      </c>
+      <c r="D41" s="12">
         <v>65</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F41" s="11">
+      <c r="F41" s="13">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G41" s="11"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B42" s="9" t="s">
         <v>81</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D42" s="10">
+        <v>275</v>
+      </c>
+      <c r="D42" s="12">
         <v>65</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F42" s="11">
+      <c r="F42" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G42" s="11"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B43" s="9" t="s">
         <v>83</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D43" s="10">
+        <v>275</v>
+      </c>
+      <c r="D43" s="12">
         <v>65</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F43" s="11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F43" s="13">
+        <v>2</v>
+      </c>
+      <c r="G43" s="11"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B44" s="9" t="s">
         <v>85</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D44" s="10">
+        <v>278</v>
+      </c>
+      <c r="D44" s="12">
         <v>145</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F44" s="11">
+      <c r="F44" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G44" s="11"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B45" s="9" t="s">
         <v>87</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D45" s="10">
+        <v>278</v>
+      </c>
+      <c r="D45" s="12">
         <v>145</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F45" s="11">
+      <c r="F45" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G45" s="11"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B46" s="9" t="s">
         <v>89</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D46" s="10">
+        <v>278</v>
+      </c>
+      <c r="D46" s="12">
         <v>145</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F46" s="11">
+      <c r="F46" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G46" s="11"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B47" s="9" t="s">
         <v>91</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D47" s="10">
+        <v>275</v>
+      </c>
+      <c r="D47" s="12">
         <v>29.8</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F47" s="11">
+      <c r="F47" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G47" s="11"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B48" s="9" t="s">
         <v>93</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D48" s="10">
+        <v>275</v>
+      </c>
+      <c r="D48" s="12">
         <v>29.8</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F48" s="11">
+      <c r="F48" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G48" s="11"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B49" s="9" t="s">
         <v>95</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D49" s="10">
+        <v>275</v>
+      </c>
+      <c r="D49" s="12">
         <v>29.8</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F49" s="11">
+      <c r="F49" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G49" s="11"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B50" s="9" t="s">
         <v>97</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D50" s="10">
+        <v>278</v>
+      </c>
+      <c r="D50" s="12">
         <v>69.150000000000006</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F50" s="11">
+      <c r="F50" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G50" s="11"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B51" s="9" t="s">
         <v>99</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D51" s="10">
+        <v>278</v>
+      </c>
+      <c r="D51" s="12">
         <v>69.150000000000006</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F51" s="11">
+      <c r="F51" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G51" s="11"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B52" s="9" t="s">
         <v>101</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D52" s="10">
+        <v>278</v>
+      </c>
+      <c r="D52" s="12">
         <v>69.150000000000006</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F52" s="11">
+      <c r="F52" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G52" s="11"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>103</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="D53" s="10">
+        <v>281</v>
+      </c>
+      <c r="D53" s="12">
         <v>150.49</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F53" s="11">
+      <c r="F53" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G53" s="11"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B54" s="9" t="s">
         <v>105</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="D54" s="10">
+        <v>281</v>
+      </c>
+      <c r="D54" s="12">
         <v>150.49</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F54" s="11">
+      <c r="F54" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G54" s="11"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>107</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="D55" s="10">
+        <v>281</v>
+      </c>
+      <c r="D55" s="12">
         <v>150.49</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="F55" s="11">
+      <c r="F55" s="13">
         <v>-2</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G55" s="11"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B56" s="9" t="s">
         <v>109</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D56" s="10">
+        <v>279</v>
+      </c>
+      <c r="D56" s="12">
         <v>35</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="F56" s="11">
+      <c r="F56" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G56" s="11"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B57" s="9" t="s">
         <v>111</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D57" s="10">
+        <v>279</v>
+      </c>
+      <c r="D57" s="12">
         <v>35</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="F57" s="11">
+      <c r="F57" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G57" s="11"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B58" s="9" t="s">
         <v>113</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D58" s="10">
+        <v>279</v>
+      </c>
+      <c r="D58" s="12">
         <v>35</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F58" s="11">
+      <c r="F58" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G58" s="11"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B59" s="9" t="s">
         <v>115</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D59" s="10">
+        <v>278</v>
+      </c>
+      <c r="D59" s="12">
         <v>151</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F59" s="11">
+      <c r="F59" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G59" s="11"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B60" s="9" t="s">
         <v>117</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D60" s="10">
+        <v>278</v>
+      </c>
+      <c r="D60" s="12">
         <v>151</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F60" s="11">
+      <c r="F60" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G60" s="11"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B61" s="9" t="s">
         <v>119</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D61" s="10">
+        <v>278</v>
+      </c>
+      <c r="D61" s="12">
         <v>151</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F61" s="11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F61" s="13">
+        <v>3</v>
+      </c>
+      <c r="G61" s="11"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B62" s="9" t="s">
         <v>121</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D62" s="10">
+        <v>279</v>
+      </c>
+      <c r="D62" s="12">
         <v>37</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F62" s="11">
+      <c r="F62" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G62" s="11"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B63" s="9" t="s">
         <v>123</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D63" s="10">
+        <v>279</v>
+      </c>
+      <c r="D63" s="12">
         <v>37</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="F63" s="11">
+      <c r="F63" s="13">
         <v>6</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G63" s="11"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B64" s="9" t="s">
         <v>125</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D64" s="10">
+        <v>279</v>
+      </c>
+      <c r="D64" s="12">
         <v>37</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="F64" s="11">
+      <c r="F64" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G64" s="11"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>127</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D65" s="10">
+        <v>275</v>
+      </c>
+      <c r="D65" s="12">
         <v>42.300000000000004</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="F65" s="11">
+      <c r="F65" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G65" s="11"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B66" s="9" t="s">
         <v>129</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D66" s="10">
+        <v>275</v>
+      </c>
+      <c r="D66" s="12">
         <v>42.300000000000004</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="F66" s="11">
+      <c r="F66" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G66" s="11"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B67" s="9" t="s">
         <v>131</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D67" s="10">
+        <v>275</v>
+      </c>
+      <c r="D67" s="12">
         <v>42.300000000000004</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="F67" s="11">
+      <c r="F67" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G67" s="11"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B68" s="9" t="s">
         <v>133</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D68" s="10">
+        <v>278</v>
+      </c>
+      <c r="D68" s="12">
         <v>109.49000000000001</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="F68" s="11">
+      <c r="F68" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G68" s="11"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B69" s="9" t="s">
         <v>135</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D69" s="10">
+        <v>278</v>
+      </c>
+      <c r="D69" s="12">
         <v>96.850000000000009</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="F69" s="11">
+      <c r="F69" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G69" s="11"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B70" s="9" t="s">
         <v>137</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D70" s="10">
+        <v>278</v>
+      </c>
+      <c r="D70" s="12">
         <v>96.850000000000009</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="F70" s="11">
+      <c r="F70" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G70" s="11"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B71" s="9" t="s">
         <v>139</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D71" s="10">
+        <v>279</v>
+      </c>
+      <c r="D71" s="12">
         <v>37</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="F71" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F71" s="13">
+        <v>-1</v>
+      </c>
+      <c r="G71" s="11"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B72" s="9" t="s">
         <v>141</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D72" s="10">
+        <v>279</v>
+      </c>
+      <c r="D72" s="12">
         <v>34</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="F72" s="11">
+      <c r="F72" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G72" s="11"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B73" s="9" t="s">
         <v>143</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D73" s="10">
+        <v>279</v>
+      </c>
+      <c r="D73" s="12">
         <v>34</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="F73" s="11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F73" s="13">
+        <v>3</v>
+      </c>
+      <c r="G73" s="11"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B74" s="9" t="s">
         <v>145</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D74" s="10">
+        <v>275</v>
+      </c>
+      <c r="D74" s="12">
         <v>46.5</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F74" s="11">
+      <c r="F74" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G74" s="11"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B75" s="9" t="s">
         <v>147</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D75" s="10">
+        <v>275</v>
+      </c>
+      <c r="D75" s="12">
         <v>60</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="F75" s="11">
+      <c r="F75" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G75" s="11"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B76" s="9" t="s">
         <v>149</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D76" s="10">
+        <v>275</v>
+      </c>
+      <c r="D76" s="12">
         <v>60</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="F76" s="11">
+      <c r="F76" s="13">
         <v>7</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G76" s="11"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B77" s="9" t="s">
         <v>151</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D77" s="10">
+        <v>278</v>
+      </c>
+      <c r="D77" s="12">
         <v>136</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="F77" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F77" s="13">
+        <v>1</v>
+      </c>
+      <c r="G77" s="11"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B78" s="9" t="s">
         <v>153</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D78" s="10">
+        <v>278</v>
+      </c>
+      <c r="D78" s="12">
         <v>136</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F78" s="11">
+      <c r="F78" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G78" s="11"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B79" s="9" t="s">
         <v>155</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D79" s="10">
+        <v>278</v>
+      </c>
+      <c r="D79" s="12">
         <v>136</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="F79" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F79" s="13">
+        <v>-1</v>
+      </c>
+      <c r="G79" s="11"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B80" s="9" t="s">
         <v>157</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D80" s="10">
+        <v>275</v>
+      </c>
+      <c r="D80" s="12">
         <v>53</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="F80" s="11">
+      <c r="F80" s="13">
         <v>4</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G80" s="11"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B81" s="9" t="s">
         <v>159</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D81" s="10">
+        <v>275</v>
+      </c>
+      <c r="D81" s="12">
         <v>53</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="F81" s="11">
+      <c r="F81" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G81" s="11"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B82" s="9" t="s">
         <v>161</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D82" s="10">
+        <v>278</v>
+      </c>
+      <c r="D82" s="12">
         <v>123</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="F82" s="11">
+      <c r="F82" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G82" s="11"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B83" s="9" t="s">
         <v>163</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D83" s="10">
+        <v>278</v>
+      </c>
+      <c r="D83" s="12">
         <v>123</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="F83" s="11">
+      <c r="F83" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G83" s="11"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B84" s="9" t="s">
         <v>165</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="D84" s="10">
+        <v>287</v>
+      </c>
+      <c r="D84" s="12">
         <v>36</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="F84" s="11">
+      <c r="F84" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G84" s="11"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B85" s="9" t="s">
         <v>165</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D85" s="10">
+        <v>276</v>
+      </c>
+      <c r="D85" s="12">
         <v>107</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="F85" s="11">
+      <c r="F85" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G85" s="11"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B86" s="9" t="s">
         <v>168</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D86" s="10">
+        <v>275</v>
+      </c>
+      <c r="D86" s="12">
         <v>39.5</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="F86" s="11">
+      <c r="F86" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G86" s="11"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B87" s="9" t="s">
         <v>170</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D87" s="10">
+        <v>275</v>
+      </c>
+      <c r="D87" s="12">
         <v>39.5</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="F87" s="11">
+      <c r="F87" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G87" s="11"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B88" s="9" t="s">
         <v>172</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D88" s="10">
+        <v>278</v>
+      </c>
+      <c r="D88" s="12">
         <v>90</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="F88" s="11">
+      <c r="F88" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G88" s="11"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B89" s="9" t="s">
         <v>174</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D89" s="10">
+        <v>278</v>
+      </c>
+      <c r="D89" s="12">
         <v>86</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="F89" s="11">
+      <c r="F89" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G89" s="11"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B90" s="9" t="s">
         <v>176</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D90" s="10">
+        <v>277</v>
+      </c>
+      <c r="D90" s="12">
         <v>130</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="F90" s="11">
+      <c r="F90" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G90" s="11"/>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B91" s="9" t="s">
         <v>178</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D91" s="10">
+        <v>277</v>
+      </c>
+      <c r="D91" s="12">
         <v>130</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="F91" s="11">
+      <c r="F91" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G91" s="11"/>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B92" s="9" t="s">
         <v>180</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D92" s="10">
+        <v>275</v>
+      </c>
+      <c r="D92" s="12">
         <v>34.5</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="F92" s="11">
+      <c r="F92" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G92" s="11"/>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B93" s="9" t="s">
         <v>182</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D93" s="10">
+        <v>276</v>
+      </c>
+      <c r="D93" s="12">
         <v>71.5</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F93" s="11">
+      <c r="F93" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G93" s="11"/>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B94" s="9" t="s">
         <v>184</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="D94" s="10">
+        <v>283</v>
+      </c>
+      <c r="D94" s="12">
         <v>131.5</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="F94" s="11">
+      <c r="F94" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G94" s="11"/>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B95" s="9" t="s">
         <v>186</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D95" s="10">
+        <v>275</v>
+      </c>
+      <c r="D95" s="12">
         <v>36</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="F95" s="11">
+      <c r="F95" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G95" s="11"/>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B96" s="9" t="s">
         <v>188</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D96" s="10">
+        <v>275</v>
+      </c>
+      <c r="D96" s="12">
         <v>36</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="F96" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F96" s="13">
+        <v>1</v>
+      </c>
+      <c r="G96" s="11"/>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B97" s="9" t="s">
         <v>190</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D97" s="10">
+        <v>278</v>
+      </c>
+      <c r="D97" s="12">
         <v>78</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="F97" s="11">
+      <c r="F97" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G97" s="11"/>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B98" s="9" t="s">
         <v>192</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D98" s="10">
+        <v>278</v>
+      </c>
+      <c r="D98" s="12">
         <v>78</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="F98" s="11">
+      <c r="F98" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G98" s="11"/>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B99" s="9" t="s">
         <v>194</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D99" s="10">
-        <v>145</v>
+        <v>277</v>
+      </c>
+      <c r="D99" s="12">
+        <v>150</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="F99" s="11">
+      <c r="F99" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G99" s="11"/>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B100" s="9" t="s">
         <v>196</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D100" s="10">
-        <v>145</v>
+        <v>277</v>
+      </c>
+      <c r="D100" s="12">
+        <v>150</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="F100" s="11">
+      <c r="F100" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G100" s="11"/>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B101" s="9" t="s">
         <v>198</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D101" s="10">
+        <v>276</v>
+      </c>
+      <c r="D101" s="12">
         <v>55</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="F101" s="11">
+      <c r="F101" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G101" s="11"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B102" s="9" t="s">
         <v>200</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D102" s="10">
+        <v>282</v>
+      </c>
+      <c r="D102" s="12">
         <v>35.5</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="F102" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F102" s="13">
+        <v>6</v>
+      </c>
+      <c r="G102" s="11"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B103" s="9" t="s">
         <v>202</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D103" s="10">
+        <v>282</v>
+      </c>
+      <c r="D103" s="12">
         <v>35.5</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="F103" s="11">
+      <c r="F103" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G103" s="11"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B104" s="9" t="s">
         <v>204</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D104" s="10">
+        <v>282</v>
+      </c>
+      <c r="D104" s="12">
         <v>35.5</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="F104" s="11">
+      <c r="F104" s="13">
         <v>4</v>
       </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G104" s="11"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B105" s="9" t="s">
         <v>206</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D105" s="10">
+        <v>275</v>
+      </c>
+      <c r="D105" s="12">
         <v>53.95</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="F105" s="11">
+      <c r="F105" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G105" s="11"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B106" s="9" t="s">
         <v>208</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D106" s="10">
+        <v>275</v>
+      </c>
+      <c r="D106" s="12">
         <v>59</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="F106" s="11">
+      <c r="F106" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G106" s="11"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B107" s="9" t="s">
         <v>210</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D107" s="10">
+        <v>275</v>
+      </c>
+      <c r="D107" s="12">
         <v>53.95</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F107" s="11">
+      <c r="F107" s="13">
         <v>4</v>
       </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G107" s="11"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B108" s="9" t="s">
         <v>212</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D108" s="10">
+        <v>276</v>
+      </c>
+      <c r="D108" s="12">
         <v>146</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="F108" s="11">
+      <c r="F108" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G108" s="11"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B109" s="9" t="s">
         <v>214</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D109" s="10">
+        <v>276</v>
+      </c>
+      <c r="D109" s="12">
         <v>146</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="F109" s="11">
+      <c r="F109" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G109" s="11"/>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B110" s="9" t="s">
         <v>216</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D110" s="10">
+        <v>276</v>
+      </c>
+      <c r="D110" s="12">
         <v>146</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="F110" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F110" s="13">
+        <v>1</v>
+      </c>
+      <c r="G110" s="11"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B111" s="9" t="s">
         <v>218</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D111" s="10">
+        <v>279</v>
+      </c>
+      <c r="D111" s="12">
         <v>20.5</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="F111" s="11">
+      <c r="F111" s="13">
         <v>4</v>
       </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G111" s="11"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B112" s="9" t="s">
         <v>220</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D112" s="10">
+        <v>275</v>
+      </c>
+      <c r="D112" s="12">
         <v>34.15</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="F112" s="11">
+      <c r="F112" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G112" s="11"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B113" s="9" t="s">
         <v>222</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D113" s="10">
+        <v>275</v>
+      </c>
+      <c r="D113" s="12">
         <v>34.15</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="F113" s="11">
+      <c r="F113" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G113" s="11"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B114" s="9" t="s">
         <v>224</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D114" s="10">
+        <v>278</v>
+      </c>
+      <c r="D114" s="12">
         <v>76.350000000000009</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="F114" s="11">
+      <c r="F114" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G114" s="11"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B115" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="D115" s="10">
+      <c r="D115" s="12">
         <v>6.55</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F115" s="11">
+      <c r="F115" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G115" s="11"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B116" s="9" t="s">
         <v>228</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D116" s="10">
+        <v>280</v>
+      </c>
+      <c r="D116" s="12">
         <v>8.5</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="F116" s="11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F116" s="13">
+        <v>2</v>
+      </c>
+      <c r="G116" s="11"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B117" s="9" t="s">
         <v>230</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D117" s="10">
+        <v>280</v>
+      </c>
+      <c r="D117" s="12">
         <v>8.5</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F117" s="11">
+      <c r="F117" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G117" s="11"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B118" s="9" t="s">
         <v>232</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D118" s="10">
+        <v>280</v>
+      </c>
+      <c r="D118" s="12">
         <v>8.5</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="F118" s="11">
+      <c r="F118" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G118" s="11"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B119" s="9" t="s">
         <v>234</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D119" s="10">
+        <v>275</v>
+      </c>
+      <c r="D119" s="12">
         <v>46.35</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="F119" s="11">
+      <c r="F119" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G119" s="11"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B120" s="9" t="s">
         <v>236</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D120" s="10">
+        <v>275</v>
+      </c>
+      <c r="D120" s="12">
         <v>46.35</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="F120" s="11">
+      <c r="F120" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G120" s="11"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B121" s="9" t="s">
         <v>238</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D121" s="10">
+        <v>278</v>
+      </c>
+      <c r="D121" s="12">
         <v>107.35000000000001</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F121" s="11">
+      <c r="F121" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G121" s="11"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B122" s="9" t="s">
         <v>240</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D122" s="10">
+        <v>275</v>
+      </c>
+      <c r="D122" s="12">
         <v>52</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="F122" s="11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F122" s="13">
+        <v>2</v>
+      </c>
+      <c r="G122" s="11"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B123" s="9" t="s">
         <v>242</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D123" s="10">
+        <v>275</v>
+      </c>
+      <c r="D123" s="12">
         <v>52</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="F123" s="11">
+      <c r="F123" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G123" s="11"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B124" s="9" t="s">
         <v>244</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D124" s="10">
+        <v>275</v>
+      </c>
+      <c r="D124" s="12">
         <v>52</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="F124" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F124" s="13">
+        <v>1</v>
+      </c>
+      <c r="G124" s="11"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B125" s="9" t="s">
         <v>246</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D125" s="10">
+        <v>284</v>
+      </c>
+      <c r="D125" s="12">
         <v>95.990000000000009</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="F125" s="11">
+      <c r="F125" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G125" s="11"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B126" s="9" t="s">
         <v>248</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D126" s="10">
+        <v>284</v>
+      </c>
+      <c r="D126" s="12">
         <v>114.49000000000001</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="F126" s="11">
+      <c r="F126" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G126" s="11"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B127" s="9" t="s">
         <v>250</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D127" s="10">
+        <v>284</v>
+      </c>
+      <c r="D127" s="12">
         <v>95.990000000000009</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="F127" s="11">
+      <c r="F127" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G127" s="11"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B128" s="9" t="s">
         <v>252</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D128" s="10">
+        <v>277</v>
+      </c>
+      <c r="D128" s="12">
         <v>212</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="F128" s="11">
+      <c r="F128" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G128" s="11"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B129" s="9" t="s">
         <v>254</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D129" s="10">
+        <v>277</v>
+      </c>
+      <c r="D129" s="12">
         <v>212</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="F129" s="11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F129" s="13">
+        <v>3</v>
+      </c>
+      <c r="G129" s="11"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B130" s="9" t="s">
         <v>256</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D130" s="10">
+        <v>277</v>
+      </c>
+      <c r="D130" s="12">
         <v>212</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="F130" s="11">
+      <c r="F130" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G130" s="11"/>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B131" s="9" t="s">
         <v>258</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D131" s="10">
-        <v>63.4</v>
+        <v>285</v>
+      </c>
+      <c r="D131" s="12">
+        <v>40</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="F131" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F131" s="13">
+        <v>2</v>
+      </c>
+      <c r="G131" s="11"/>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B132" s="9" t="s">
         <v>260</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="D132" s="10">
-        <v>40</v>
+        <v>284</v>
+      </c>
+      <c r="D132" s="12">
+        <v>86</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="F132" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F132" s="13">
+        <v>0</v>
+      </c>
+      <c r="G132" s="11"/>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B133" s="9" t="s">
         <v>262</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D133" s="10">
-        <v>71.989999999999995</v>
+        <v>284</v>
+      </c>
+      <c r="D133" s="12">
+        <v>108.31</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="F133" s="11">
+      <c r="F133" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G133" s="11"/>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B134" s="9" t="s">
         <v>264</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D134" s="10">
-        <v>108.31</v>
+        <v>284</v>
+      </c>
+      <c r="D134" s="12">
+        <v>73.650000000000006</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F134" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F134" s="13">
+        <v>2</v>
+      </c>
+      <c r="G134" s="11"/>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B135" s="9" t="s">
         <v>266</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D135" s="10">
-        <v>73.650000000000006</v>
+        <v>286</v>
+      </c>
+      <c r="D135" s="12">
+        <v>190</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="F135" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F135" s="13">
+        <v>1</v>
+      </c>
+      <c r="G135" s="11"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B136" s="9" t="s">
         <v>268</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D136" s="10">
-        <v>73.650000000000006</v>
+        <v>278</v>
+      </c>
+      <c r="D136" s="12">
+        <v>67</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="F136" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B137" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="D137" s="10">
-        <v>190</v>
-      </c>
-      <c r="E137" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="F137" s="11">
+      <c r="F136" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B138" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D138" s="10">
-        <v>67</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="F138" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G136" s="11"/>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E137" s="2"/>
+      <c r="F137" s="5"/>
+      <c r="G137" s="10"/>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E138" s="2"/>
+      <c r="F138" s="5"/>
+      <c r="G138" s="10"/>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E139" s="2"/>
       <c r="F139" s="5"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G139" s="10"/>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E140" s="2"/>
       <c r="F140" s="5"/>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G140" s="10"/>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E141" s="2"/>
       <c r="F141" s="5"/>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G141" s="10"/>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E142" s="2"/>
       <c r="F142" s="5"/>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G142" s="10"/>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E143" s="2"/>
       <c r="F143" s="5"/>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G143" s="10"/>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E144" s="2"/>
       <c r="F144" s="5"/>
-    </row>
-    <row r="145" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G144" s="10"/>
+    </row>
+    <row r="145" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E145" s="2"/>
       <c r="F145" s="5"/>
-    </row>
-    <row r="146" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G145" s="10"/>
+    </row>
+    <row r="146" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E146" s="2"/>
       <c r="F146" s="5"/>
-    </row>
-    <row r="147" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G146" s="10"/>
+    </row>
+    <row r="147" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E147" s="2"/>
       <c r="F147" s="5"/>
-    </row>
-    <row r="148" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G147" s="10"/>
+    </row>
+    <row r="148" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E148" s="2"/>
       <c r="F148" s="5"/>
-    </row>
-    <row r="149" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G148" s="10"/>
+    </row>
+    <row r="149" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E149" s="2"/>
       <c r="F149" s="5"/>
-    </row>
-    <row r="150" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G149" s="10"/>
+    </row>
+    <row r="150" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E150" s="2"/>
       <c r="F150" s="5"/>
-    </row>
-    <row r="151" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G150" s="10"/>
+    </row>
+    <row r="151" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E151" s="2"/>
       <c r="F151" s="5"/>
-    </row>
-    <row r="152" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G151" s="10"/>
+    </row>
+    <row r="152" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E152" s="2"/>
       <c r="F152" s="5"/>
-    </row>
-    <row r="153" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G152" s="10"/>
+    </row>
+    <row r="153" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E153" s="2"/>
       <c r="F153" s="5"/>
-    </row>
-    <row r="154" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G153" s="10"/>
+    </row>
+    <row r="154" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E154" s="2"/>
       <c r="F154" s="5"/>
-    </row>
-    <row r="155" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G154" s="10"/>
+    </row>
+    <row r="155" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E155" s="2"/>
       <c r="F155" s="5"/>
-    </row>
-    <row r="156" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G155" s="10"/>
+    </row>
+    <row r="156" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E156" s="2"/>
       <c r="F156" s="5"/>
-    </row>
-    <row r="157" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G156" s="10"/>
+    </row>
+    <row r="157" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E157" s="2"/>
       <c r="F157" s="5"/>
-    </row>
-    <row r="158" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G157" s="10"/>
+    </row>
+    <row r="158" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E158" s="2"/>
       <c r="F158" s="5"/>
-    </row>
-    <row r="159" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G158" s="10"/>
+    </row>
+    <row r="159" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E159" s="2"/>
       <c r="F159" s="5"/>
-    </row>
-    <row r="160" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G159" s="10"/>
+    </row>
+    <row r="160" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E160" s="2"/>
       <c r="F160" s="5"/>
-    </row>
-    <row r="161" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G160" s="10"/>
+    </row>
+    <row r="161" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E161" s="2"/>
       <c r="F161" s="5"/>
-    </row>
-    <row r="162" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G161" s="10"/>
+    </row>
+    <row r="162" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E162" s="2"/>
       <c r="F162" s="5"/>
-    </row>
-    <row r="163" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G162" s="10"/>
+    </row>
+    <row r="163" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E163" s="2"/>
       <c r="F163" s="5"/>
-    </row>
-    <row r="164" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G163" s="10"/>
+    </row>
+    <row r="164" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E164" s="2"/>
       <c r="F164" s="5"/>
-    </row>
-    <row r="165" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G164" s="10"/>
+    </row>
+    <row r="165" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E165" s="2"/>
       <c r="F165" s="5"/>
-    </row>
-    <row r="166" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G165" s="10"/>
+    </row>
+    <row r="166" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E166" s="2"/>
       <c r="F166" s="5"/>
-    </row>
-    <row r="167" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G166" s="10"/>
+    </row>
+    <row r="167" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E167" s="2"/>
       <c r="F167" s="5"/>
-    </row>
-    <row r="168" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G167" s="10"/>
+    </row>
+    <row r="168" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E168" s="2"/>
       <c r="F168" s="5"/>
-    </row>
-    <row r="169" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G168" s="10"/>
+    </row>
+    <row r="169" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E169" s="2"/>
       <c r="F169" s="5"/>
-    </row>
-    <row r="170" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G169" s="10"/>
+    </row>
+    <row r="170" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E170" s="2"/>
       <c r="F170" s="5"/>
-    </row>
-    <row r="171" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G170" s="10"/>
+    </row>
+    <row r="171" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E171" s="2"/>
       <c r="F171" s="5"/>
-    </row>
-    <row r="172" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G171" s="10"/>
+    </row>
+    <row r="172" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E172" s="2"/>
       <c r="F172" s="5"/>
-    </row>
-    <row r="173" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G172" s="10"/>
+    </row>
+    <row r="173" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E173" s="2"/>
       <c r="F173" s="5"/>
-    </row>
-    <row r="174" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G173" s="10"/>
+    </row>
+    <row r="174" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E174" s="2"/>
       <c r="F174" s="5"/>
-    </row>
-    <row r="175" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G174" s="10"/>
+    </row>
+    <row r="175" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E175" s="2"/>
       <c r="F175" s="5"/>
-    </row>
-    <row r="176" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G175" s="10"/>
+    </row>
+    <row r="176" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E176" s="2"/>
       <c r="F176" s="5"/>
-    </row>
-    <row r="177" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G176" s="10"/>
+    </row>
+    <row r="177" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E177" s="2"/>
       <c r="F177" s="5"/>
-    </row>
-    <row r="178" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G177" s="10"/>
+    </row>
+    <row r="178" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E178" s="2"/>
       <c r="F178" s="5"/>
-    </row>
-    <row r="179" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G178" s="10"/>
+    </row>
+    <row r="179" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E179" s="2"/>
       <c r="F179" s="5"/>
-    </row>
-    <row r="180" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G179" s="10"/>
+    </row>
+    <row r="180" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E180" s="2"/>
       <c r="F180" s="5"/>
-    </row>
-    <row r="181" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G180" s="10"/>
+    </row>
+    <row r="181" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E181" s="2"/>
       <c r="F181" s="5"/>
-    </row>
-    <row r="182" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G181" s="10"/>
+    </row>
+    <row r="182" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E182" s="2"/>
       <c r="F182" s="5"/>
-    </row>
-    <row r="183" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G182" s="10"/>
+    </row>
+    <row r="183" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E183" s="2"/>
       <c r="F183" s="5"/>
-    </row>
-    <row r="184" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G183" s="10"/>
+    </row>
+    <row r="184" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E184" s="2"/>
       <c r="F184" s="5"/>
-    </row>
-    <row r="185" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G184" s="10"/>
+    </row>
+    <row r="185" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E185" s="2"/>
       <c r="F185" s="5"/>
-    </row>
-    <row r="186" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G185" s="10"/>
+    </row>
+    <row r="186" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E186" s="2"/>
       <c r="F186" s="5"/>
-    </row>
-    <row r="187" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G186" s="10"/>
+    </row>
+    <row r="187" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E187" s="2"/>
       <c r="F187" s="5"/>
-    </row>
-    <row r="188" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G187" s="10"/>
+    </row>
+    <row r="188" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E188" s="2"/>
       <c r="F188" s="5"/>
-    </row>
-    <row r="189" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G188" s="10"/>
+    </row>
+    <row r="189" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E189" s="2"/>
       <c r="F189" s="5"/>
-    </row>
-    <row r="190" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G189" s="10"/>
+    </row>
+    <row r="190" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E190" s="2"/>
       <c r="F190" s="5"/>
-    </row>
-    <row r="191" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G190" s="10"/>
+    </row>
+    <row r="191" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E191" s="2"/>
       <c r="F191" s="5"/>
-    </row>
-    <row r="192" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G191" s="10"/>
+    </row>
+    <row r="192" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E192" s="2"/>
       <c r="F192" s="5"/>
-    </row>
-    <row r="193" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G192" s="10"/>
+    </row>
+    <row r="193" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E193" s="2"/>
       <c r="F193" s="5"/>
-    </row>
-    <row r="194" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G193" s="10"/>
+    </row>
+    <row r="194" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E194" s="2"/>
       <c r="F194" s="5"/>
-    </row>
-    <row r="195" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G194" s="10"/>
+    </row>
+    <row r="195" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E195" s="2"/>
       <c r="F195" s="5"/>
-    </row>
-    <row r="196" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G195" s="10"/>
+    </row>
+    <row r="196" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E196" s="2"/>
       <c r="F196" s="5"/>
-    </row>
-    <row r="197" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G196" s="10"/>
+    </row>
+    <row r="197" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E197" s="2"/>
       <c r="F197" s="5"/>
-    </row>
-    <row r="198" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G197" s="10"/>
+    </row>
+    <row r="198" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E198" s="2"/>
       <c r="F198" s="5"/>
-    </row>
-    <row r="199" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G198" s="10"/>
+    </row>
+    <row r="199" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E199" s="2"/>
       <c r="F199" s="5"/>
-    </row>
-    <row r="200" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G199" s="10"/>
+    </row>
+    <row r="200" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E200" s="2"/>
       <c r="F200" s="5"/>
-    </row>
-    <row r="201" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G200" s="10"/>
+    </row>
+    <row r="201" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E201" s="2"/>
       <c r="F201" s="5"/>
-    </row>
-    <row r="202" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G201" s="10"/>
+    </row>
+    <row r="202" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E202" s="2"/>
       <c r="F202" s="5"/>
-    </row>
-    <row r="203" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G202" s="10"/>
+    </row>
+    <row r="203" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E203" s="2"/>
       <c r="F203" s="5"/>
-    </row>
-    <row r="204" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G203" s="10"/>
+    </row>
+    <row r="204" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E204" s="2"/>
       <c r="F204" s="5"/>
-    </row>
-    <row r="205" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G204" s="10"/>
+    </row>
+    <row r="205" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E205" s="2"/>
       <c r="F205" s="5"/>
-    </row>
-    <row r="206" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G205" s="10"/>
+    </row>
+    <row r="206" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E206" s="2"/>
       <c r="F206" s="5"/>
-    </row>
-    <row r="207" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G206" s="10"/>
+    </row>
+    <row r="207" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E207" s="2"/>
       <c r="F207" s="5"/>
-    </row>
-    <row r="208" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G207" s="10"/>
+    </row>
+    <row r="208" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E208" s="2"/>
       <c r="F208" s="5"/>
-    </row>
-    <row r="209" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G208" s="10"/>
+    </row>
+    <row r="209" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E209" s="2"/>
       <c r="F209" s="5"/>
-    </row>
-    <row r="210" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G209" s="10"/>
+    </row>
+    <row r="210" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E210" s="2"/>
       <c r="F210" s="5"/>
-    </row>
-    <row r="211" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G210" s="10"/>
+    </row>
+    <row r="211" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E211" s="2"/>
       <c r="F211" s="5"/>
-    </row>
-    <row r="212" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G211" s="10"/>
+    </row>
+    <row r="212" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E212" s="2"/>
       <c r="F212" s="5"/>
-    </row>
-    <row r="213" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G212" s="10"/>
+    </row>
+    <row r="213" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E213" s="2"/>
       <c r="F213" s="5"/>
-    </row>
-    <row r="214" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G213" s="10"/>
+    </row>
+    <row r="214" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E214" s="2"/>
       <c r="F214" s="5"/>
-    </row>
-    <row r="215" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G214" s="10"/>
+    </row>
+    <row r="215" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E215" s="2"/>
       <c r="F215" s="5"/>
-    </row>
-    <row r="216" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G215" s="10"/>
+    </row>
+    <row r="216" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E216" s="2"/>
       <c r="F216" s="5"/>
-    </row>
-    <row r="217" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G216" s="10"/>
+    </row>
+    <row r="217" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E217" s="2"/>
       <c r="F217" s="5"/>
-    </row>
-    <row r="218" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G217" s="10"/>
+    </row>
+    <row r="218" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E218" s="2"/>
       <c r="F218" s="5"/>
-    </row>
-    <row r="219" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G218" s="10"/>
+    </row>
+    <row r="219" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E219" s="2"/>
       <c r="F219" s="5"/>
-    </row>
-    <row r="220" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G219" s="10"/>
+    </row>
+    <row r="220" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E220" s="2"/>
       <c r="F220" s="5"/>
-    </row>
-    <row r="221" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G220" s="10"/>
+    </row>
+    <row r="221" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E221" s="2"/>
       <c r="F221" s="5"/>
-    </row>
-    <row r="222" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G221" s="10"/>
+    </row>
+    <row r="222" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E222" s="2"/>
       <c r="F222" s="5"/>
-    </row>
-    <row r="223" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G222" s="10"/>
+    </row>
+    <row r="223" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E223" s="2"/>
       <c r="F223" s="5"/>
-    </row>
-    <row r="224" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G223" s="10"/>
+    </row>
+    <row r="224" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E224" s="2"/>
       <c r="F224" s="5"/>
-    </row>
-    <row r="225" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G224" s="10"/>
+    </row>
+    <row r="225" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E225" s="2"/>
       <c r="F225" s="5"/>
-    </row>
-    <row r="226" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G225" s="10"/>
+    </row>
+    <row r="226" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E226" s="2"/>
       <c r="F226" s="5"/>
-    </row>
-    <row r="227" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G226" s="10"/>
+    </row>
+    <row r="227" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E227" s="2"/>
       <c r="F227" s="5"/>
-    </row>
-    <row r="228" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G227" s="10"/>
+    </row>
+    <row r="228" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E228" s="2"/>
       <c r="F228" s="5"/>
-    </row>
-    <row r="229" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G228" s="10"/>
+    </row>
+    <row r="229" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E229" s="2"/>
       <c r="F229" s="5"/>
-    </row>
-    <row r="230" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G229" s="10"/>
+    </row>
+    <row r="230" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E230" s="2"/>
       <c r="F230" s="5"/>
-    </row>
-    <row r="231" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G230" s="10"/>
+    </row>
+    <row r="231" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E231" s="2"/>
       <c r="F231" s="5"/>
-    </row>
-    <row r="232" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G231" s="10"/>
+    </row>
+    <row r="232" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E232" s="2"/>
       <c r="F232" s="5"/>
-    </row>
-    <row r="233" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G232" s="10"/>
+    </row>
+    <row r="233" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E233" s="2"/>
       <c r="F233" s="5"/>
-    </row>
-    <row r="234" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G233" s="10"/>
+    </row>
+    <row r="234" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E234" s="2"/>
       <c r="F234" s="5"/>
-    </row>
-    <row r="235" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G234" s="10"/>
+    </row>
+    <row r="235" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E235" s="2"/>
       <c r="F235" s="5"/>
-    </row>
-    <row r="236" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G235" s="10"/>
+    </row>
+    <row r="236" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E236" s="2"/>
       <c r="F236" s="5"/>
-    </row>
-    <row r="237" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G236" s="10"/>
+    </row>
+    <row r="237" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E237" s="2"/>
       <c r="F237" s="5"/>
-    </row>
-    <row r="238" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G237" s="10"/>
+    </row>
+    <row r="238" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E238" s="2"/>
       <c r="F238" s="5"/>
-    </row>
-    <row r="239" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G238" s="10"/>
+    </row>
+    <row r="239" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E239" s="2"/>
       <c r="F239" s="5"/>
-    </row>
-    <row r="240" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G239" s="10"/>
+    </row>
+    <row r="240" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E240" s="2"/>
       <c r="F240" s="5"/>
-    </row>
-    <row r="241" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G240" s="10"/>
+    </row>
+    <row r="241" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E241" s="2"/>
       <c r="F241" s="5"/>
-    </row>
-    <row r="242" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G241" s="10"/>
+    </row>
+    <row r="242" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E242" s="2"/>
       <c r="F242" s="5"/>
-    </row>
-    <row r="243" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G242" s="10"/>
+    </row>
+    <row r="243" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E243" s="2"/>
       <c r="F243" s="5"/>
-    </row>
-    <row r="244" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G243" s="10"/>
+    </row>
+    <row r="244" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E244" s="2"/>
       <c r="F244" s="5"/>
-    </row>
-    <row r="245" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G244" s="10"/>
+    </row>
+    <row r="245" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E245" s="2"/>
       <c r="F245" s="5"/>
-    </row>
-    <row r="246" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G245" s="10"/>
+    </row>
+    <row r="246" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E246" s="2"/>
       <c r="F246" s="5"/>
-    </row>
-    <row r="247" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G246" s="10"/>
+    </row>
+    <row r="247" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E247" s="2"/>
       <c r="F247" s="5"/>
-    </row>
-    <row r="248" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G247" s="10"/>
+    </row>
+    <row r="248" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E248" s="2"/>
       <c r="F248" s="5"/>
-    </row>
-    <row r="249" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G248" s="10"/>
+    </row>
+    <row r="249" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E249" s="2"/>
       <c r="F249" s="5"/>
-    </row>
-    <row r="250" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G249" s="10"/>
+    </row>
+    <row r="250" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E250" s="2"/>
       <c r="F250" s="5"/>
-    </row>
-    <row r="251" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G250" s="10"/>
+    </row>
+    <row r="251" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E251" s="2"/>
       <c r="F251" s="5"/>
-    </row>
-    <row r="252" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G251" s="10"/>
+    </row>
+    <row r="252" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E252" s="2"/>
       <c r="F252" s="5"/>
-    </row>
-    <row r="253" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G252" s="10"/>
+    </row>
+    <row r="253" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E253" s="2"/>
       <c r="F253" s="5"/>
-    </row>
-    <row r="254" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G253" s="10"/>
+    </row>
+    <row r="254" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E254" s="2"/>
       <c r="F254" s="5"/>
-    </row>
-    <row r="255" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G254" s="10"/>
+    </row>
+    <row r="255" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E255" s="2"/>
       <c r="F255" s="5"/>
-    </row>
-    <row r="256" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G255" s="10"/>
+    </row>
+    <row r="256" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E256" s="2"/>
       <c r="F256" s="5"/>
-    </row>
-    <row r="257" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G256" s="10"/>
+    </row>
+    <row r="257" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E257" s="2"/>
       <c r="F257" s="5"/>
-    </row>
-    <row r="258" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G257" s="10"/>
+    </row>
+    <row r="258" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E258" s="2"/>
       <c r="F258" s="5"/>
-    </row>
-    <row r="259" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G258" s="10"/>
+    </row>
+    <row r="259" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E259" s="2"/>
       <c r="F259" s="5"/>
-    </row>
-    <row r="260" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G259" s="10"/>
+    </row>
+    <row r="260" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E260" s="2"/>
       <c r="F260" s="5"/>
-    </row>
-    <row r="261" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G260" s="10"/>
+    </row>
+    <row r="261" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E261" s="2"/>
       <c r="F261" s="5"/>
-    </row>
-    <row r="262" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G261" s="10"/>
+    </row>
+    <row r="262" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E262" s="2"/>
       <c r="F262" s="5"/>
-    </row>
-    <row r="263" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G262" s="10"/>
+    </row>
+    <row r="263" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E263" s="2"/>
       <c r="F263" s="5"/>
-    </row>
-    <row r="264" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G263" s="10"/>
+    </row>
+    <row r="264" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E264" s="2"/>
       <c r="F264" s="5"/>
-    </row>
-    <row r="265" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G264" s="10"/>
+    </row>
+    <row r="265" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E265" s="2"/>
       <c r="F265" s="5"/>
-    </row>
-    <row r="266" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G265" s="10"/>
+    </row>
+    <row r="266" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E266" s="2"/>
       <c r="F266" s="5"/>
-    </row>
-    <row r="267" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G266" s="10"/>
+    </row>
+    <row r="267" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E267" s="2"/>
       <c r="F267" s="5"/>
-    </row>
-    <row r="268" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G267" s="10"/>
+    </row>
+    <row r="268" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E268" s="2"/>
       <c r="F268" s="5"/>
-    </row>
-    <row r="269" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G268" s="10"/>
+    </row>
+    <row r="269" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E269" s="2"/>
       <c r="F269" s="5"/>
-    </row>
-    <row r="270" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G269" s="10"/>
+    </row>
+    <row r="270" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E270" s="2"/>
       <c r="F270" s="5"/>
-    </row>
-    <row r="271" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G270" s="10"/>
+    </row>
+    <row r="271" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E271" s="2"/>
       <c r="F271" s="5"/>
-    </row>
-    <row r="272" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G271" s="10"/>
+    </row>
+    <row r="272" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E272" s="2"/>
       <c r="F272" s="5"/>
-    </row>
-    <row r="273" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G272" s="10"/>
+    </row>
+    <row r="273" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E273" s="2"/>
       <c r="F273" s="5"/>
-    </row>
-    <row r="274" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G273" s="10"/>
+    </row>
+    <row r="274" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E274" s="2"/>
       <c r="F274" s="5"/>
-    </row>
-    <row r="275" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G274" s="10"/>
+    </row>
+    <row r="275" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E275" s="2"/>
       <c r="F275" s="5"/>
-    </row>
-    <row r="276" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G275" s="10"/>
+    </row>
+    <row r="276" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E276" s="2"/>
       <c r="F276" s="5"/>
-    </row>
-    <row r="277" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G276" s="10"/>
+    </row>
+    <row r="277" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E277" s="2"/>
       <c r="F277" s="5"/>
-    </row>
-    <row r="278" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G277" s="10"/>
+    </row>
+    <row r="278" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E278" s="2"/>
       <c r="F278" s="5"/>
-    </row>
-    <row r="279" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G278" s="10"/>
+    </row>
+    <row r="279" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E279" s="2"/>
       <c r="F279" s="5"/>
-    </row>
-    <row r="280" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G279" s="10"/>
+    </row>
+    <row r="280" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E280" s="2"/>
       <c r="F280" s="5"/>
-    </row>
-    <row r="281" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G280" s="10"/>
+    </row>
+    <row r="281" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E281" s="2"/>
       <c r="F281" s="5"/>
-    </row>
-    <row r="282" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G281" s="10"/>
+    </row>
+    <row r="282" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E282" s="2"/>
       <c r="F282" s="5"/>
-    </row>
-    <row r="283" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G282" s="10"/>
+    </row>
+    <row r="283" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E283" s="2"/>
       <c r="F283" s="5"/>
-    </row>
-    <row r="284" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G283" s="10"/>
+    </row>
+    <row r="284" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E284" s="2"/>
       <c r="F284" s="5"/>
-    </row>
-    <row r="285" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G284" s="10"/>
+    </row>
+    <row r="285" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E285" s="2"/>
       <c r="F285" s="5"/>
-    </row>
-    <row r="286" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G285" s="10"/>
+    </row>
+    <row r="286" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E286" s="2"/>
       <c r="F286" s="5"/>
-    </row>
-    <row r="287" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G286" s="10"/>
+    </row>
+    <row r="287" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E287" s="2"/>
       <c r="F287" s="5"/>
-    </row>
-    <row r="288" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G287" s="10"/>
+    </row>
+    <row r="288" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E288" s="2"/>
       <c r="F288" s="5"/>
-    </row>
-    <row r="289" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G288" s="10"/>
+    </row>
+    <row r="289" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E289" s="2"/>
       <c r="F289" s="5"/>
-    </row>
-    <row r="290" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G289" s="10"/>
+    </row>
+    <row r="290" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E290" s="2"/>
       <c r="F290" s="5"/>
-    </row>
-    <row r="291" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G290" s="10"/>
+    </row>
+    <row r="291" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E291" s="2"/>
       <c r="F291" s="5"/>
-    </row>
-    <row r="292" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G291" s="10"/>
+    </row>
+    <row r="292" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E292" s="2"/>
       <c r="F292" s="5"/>
-    </row>
-    <row r="293" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G292" s="10"/>
+    </row>
+    <row r="293" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E293" s="2"/>
       <c r="F293" s="5"/>
-    </row>
-    <row r="294" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G293" s="10"/>
+    </row>
+    <row r="294" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E294" s="2"/>
       <c r="F294" s="5"/>
-    </row>
-    <row r="295" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G294" s="10"/>
+    </row>
+    <row r="295" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E295" s="2"/>
       <c r="F295" s="5"/>
-    </row>
-    <row r="296" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G295" s="10"/>
+    </row>
+    <row r="296" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E296" s="2"/>
       <c r="F296" s="5"/>
-    </row>
-    <row r="297" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G296" s="10"/>
+    </row>
+    <row r="297" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E297" s="2"/>
       <c r="F297" s="5"/>
-    </row>
-    <row r="298" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G297" s="10"/>
+    </row>
+    <row r="298" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E298" s="2"/>
       <c r="F298" s="5"/>
-    </row>
-    <row r="299" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G298" s="10"/>
+    </row>
+    <row r="299" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E299" s="2"/>
       <c r="F299" s="5"/>
-    </row>
-    <row r="300" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G299" s="10"/>
+    </row>
+    <row r="300" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E300" s="2"/>
       <c r="F300" s="5"/>
-    </row>
-    <row r="301" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="G300" s="10"/>
+    </row>
+    <row r="301" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E301" s="2"/>
       <c r="F301" s="5"/>
     </row>
-    <row r="302" spans="5:6" x14ac:dyDescent="0.3">
+    <row r="302" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E302" s="2"/>
       <c r="F302" s="5"/>
     </row>
-    <row r="303" spans="5:6" x14ac:dyDescent="0.3">
+    <row r="303" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E303" s="2"/>
       <c r="F303" s="5"/>
     </row>
-    <row r="304" spans="5:6" x14ac:dyDescent="0.3">
+    <row r="304" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E304" s="2"/>
       <c r="F304" s="5"/>
     </row>
@@ -5324,14 +5591,6 @@
     <row r="444" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E444" s="2"/>
       <c r="F444" s="5"/>
-    </row>
-    <row r="445" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E445" s="2"/>
-      <c r="F445" s="5"/>
-    </row>
-    <row r="446" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E446" s="2"/>
-      <c r="F446" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/prix/levis.xlsx
+++ b/prix/levis.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B7C67DC-F16B-4A12-AA15-5FF52FF0E67C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358CFD79-8914-4F49-BEED-61F94E96744B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -1009,7 +1009,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1035,9 +1035,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1425,16 +1422,16 @@
       <c r="C2" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="11">
         <v>45</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="13">
+      <c r="F2" s="12">
         <v>7</v>
       </c>
-      <c r="G2" s="11"/>
+      <c r="G2" s="10"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -1446,16 +1443,16 @@
       <c r="C3" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="11">
         <v>45</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="12">
         <v>8</v>
       </c>
-      <c r="G3" s="11"/>
+      <c r="G3" s="10"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -1467,16 +1464,16 @@
       <c r="C4" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="11">
         <v>94</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="12">
         <v>6</v>
       </c>
-      <c r="G4" s="11"/>
+      <c r="G4" s="10"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -1488,16 +1485,16 @@
       <c r="C5" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="11">
         <v>94</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="12">
         <v>4</v>
       </c>
-      <c r="G5" s="11"/>
+      <c r="G5" s="10"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -1509,16 +1506,16 @@
       <c r="C6" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="11">
         <v>175</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="12">
         <v>6</v>
       </c>
-      <c r="G6" s="11"/>
+      <c r="G6" s="10"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -1530,16 +1527,16 @@
       <c r="C7" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="11">
         <v>175</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="12">
         <v>1</v>
       </c>
-      <c r="G7" s="11"/>
+      <c r="G7" s="10"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -1551,16 +1548,16 @@
       <c r="C8" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="11">
         <v>175</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="12">
         <v>4</v>
       </c>
-      <c r="G8" s="11"/>
+      <c r="G8" s="10"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -1572,16 +1569,16 @@
       <c r="C9" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="11">
         <v>47.25</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="12">
         <v>0</v>
       </c>
-      <c r="G9" s="11"/>
+      <c r="G9" s="10"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -1593,16 +1590,16 @@
       <c r="C10" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <v>45</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="13">
-        <v>4</v>
-      </c>
-      <c r="G10" s="11"/>
+      <c r="F10" s="12">
+        <v>3</v>
+      </c>
+      <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -1614,16 +1611,16 @@
       <c r="C11" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="11">
         <v>45</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="12">
         <v>0</v>
       </c>
-      <c r="G11" s="11"/>
+      <c r="G11" s="10"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -1635,16 +1632,16 @@
       <c r="C12" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="11">
         <v>45</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="12">
         <v>4</v>
       </c>
-      <c r="G12" s="11"/>
+      <c r="G12" s="10"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -1656,16 +1653,16 @@
       <c r="C13" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="11">
         <v>94</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="12">
         <v>2</v>
       </c>
-      <c r="G13" s="11"/>
+      <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -1677,16 +1674,16 @@
       <c r="C14" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="11">
         <v>94</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="12">
         <v>0</v>
       </c>
-      <c r="G14" s="11"/>
+      <c r="G14" s="10"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -1698,16 +1695,16 @@
       <c r="C15" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="11">
         <v>94</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="12">
         <v>2</v>
       </c>
-      <c r="G15" s="11"/>
+      <c r="G15" s="10"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -1719,16 +1716,16 @@
       <c r="C16" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="11">
         <v>175</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="12">
         <v>3</v>
       </c>
-      <c r="G16" s="11"/>
+      <c r="G16" s="10"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
@@ -1740,16 +1737,16 @@
       <c r="C17" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="11">
         <v>175</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="12">
         <v>0</v>
       </c>
-      <c r="G17" s="11"/>
+      <c r="G17" s="10"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
@@ -1761,16 +1758,16 @@
       <c r="C18" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="11">
         <v>175</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="12">
         <v>6</v>
       </c>
-      <c r="G18" s="11"/>
+      <c r="G18" s="10"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B19" s="9" t="s">
@@ -1779,16 +1776,16 @@
       <c r="C19" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="11">
         <v>46.95</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="12">
         <v>0</v>
       </c>
-      <c r="G19" s="11"/>
+      <c r="G19" s="10"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
@@ -1800,16 +1797,16 @@
       <c r="C20" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="11">
         <v>32</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="12">
         <v>1</v>
       </c>
-      <c r="G20" s="11"/>
+      <c r="G20" s="10"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
@@ -1821,16 +1818,16 @@
       <c r="C21" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="11">
         <v>32</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="12">
         <v>3</v>
       </c>
-      <c r="G21" s="11"/>
+      <c r="G21" s="10"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
@@ -1842,16 +1839,16 @@
       <c r="C22" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="11">
         <v>32</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="12">
         <v>3</v>
       </c>
-      <c r="G22" s="11"/>
+      <c r="G22" s="10"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
@@ -1863,16 +1860,16 @@
       <c r="C23" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="11">
         <v>58</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="12">
         <v>0</v>
       </c>
-      <c r="G23" s="11"/>
+      <c r="G23" s="10"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
@@ -1884,16 +1881,16 @@
       <c r="C24" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="11">
         <v>58</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F24" s="13">
+      <c r="F24" s="12">
         <v>3</v>
       </c>
-      <c r="G24" s="11"/>
+      <c r="G24" s="10"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
@@ -1905,16 +1902,16 @@
       <c r="C25" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D25" s="12">
+      <c r="D25" s="11">
         <v>58</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F25" s="13">
+      <c r="F25" s="12">
         <v>2</v>
       </c>
-      <c r="G25" s="11"/>
+      <c r="G25" s="10"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
@@ -1926,16 +1923,16 @@
       <c r="C26" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D26" s="12">
+      <c r="D26" s="11">
         <v>135.5</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="12">
         <v>2</v>
       </c>
-      <c r="G26" s="11"/>
+      <c r="G26" s="10"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
@@ -1947,16 +1944,16 @@
       <c r="C27" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D27" s="12">
+      <c r="D27" s="11">
         <v>135.5</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F27" s="13">
+      <c r="F27" s="12">
         <v>3</v>
       </c>
-      <c r="G27" s="11"/>
+      <c r="G27" s="10"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
@@ -1968,16 +1965,16 @@
       <c r="C28" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D28" s="12">
+      <c r="D28" s="11">
         <v>135.5</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="13">
+      <c r="F28" s="12">
         <v>7</v>
       </c>
-      <c r="G28" s="11"/>
+      <c r="G28" s="10"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
@@ -1989,16 +1986,16 @@
       <c r="C29" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D29" s="12">
+      <c r="D29" s="11">
         <v>36</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F29" s="13">
-        <v>3</v>
-      </c>
-      <c r="G29" s="11"/>
+      <c r="F29" s="12">
+        <v>2</v>
+      </c>
+      <c r="G29" s="10"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
@@ -2010,16 +2007,16 @@
       <c r="C30" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" s="11">
         <v>36</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="13">
+      <c r="F30" s="12">
         <v>6</v>
       </c>
-      <c r="G30" s="11"/>
+      <c r="G30" s="10"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
@@ -2031,16 +2028,16 @@
       <c r="C31" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D31" s="12">
+      <c r="D31" s="11">
         <v>37</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F31" s="13">
-        <v>8</v>
-      </c>
-      <c r="G31" s="11"/>
+      <c r="F31" s="12">
+        <v>12</v>
+      </c>
+      <c r="G31" s="10"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
@@ -2052,16 +2049,16 @@
       <c r="C32" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D32" s="12">
+      <c r="D32" s="11">
         <v>65</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F32" s="13">
-        <v>3</v>
-      </c>
-      <c r="G32" s="11"/>
+      <c r="F32" s="12">
+        <v>2</v>
+      </c>
+      <c r="G32" s="10"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
@@ -2073,16 +2070,16 @@
       <c r="C33" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D33" s="12">
+      <c r="D33" s="11">
         <v>65</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F33" s="13">
+      <c r="F33" s="12">
         <v>1</v>
       </c>
-      <c r="G33" s="11"/>
+      <c r="G33" s="10"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
@@ -2094,16 +2091,16 @@
       <c r="C34" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D34" s="12">
+      <c r="D34" s="11">
         <v>65</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F34" s="13">
+      <c r="F34" s="12">
         <v>8</v>
       </c>
-      <c r="G34" s="11"/>
+      <c r="G34" s="10"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
@@ -2115,16 +2112,16 @@
       <c r="C35" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D35" s="12">
+      <c r="D35" s="11">
         <v>150</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F35" s="13">
+      <c r="F35" s="12">
         <v>6</v>
       </c>
-      <c r="G35" s="11"/>
+      <c r="G35" s="10"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
@@ -2136,16 +2133,16 @@
       <c r="C36" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D36" s="12">
+      <c r="D36" s="11">
         <v>150</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F36" s="13">
+      <c r="F36" s="12">
         <v>0</v>
       </c>
-      <c r="G36" s="11"/>
+      <c r="G36" s="10"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
@@ -2157,16 +2154,16 @@
       <c r="C37" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D37" s="12">
+      <c r="D37" s="11">
         <v>150</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F37" s="13">
+      <c r="F37" s="12">
         <v>5</v>
       </c>
-      <c r="G37" s="11"/>
+      <c r="G37" s="10"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
@@ -2178,16 +2175,16 @@
       <c r="C38" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D38" s="12">
+      <c r="D38" s="11">
         <v>36</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F38" s="13">
+      <c r="F38" s="12">
         <v>7</v>
       </c>
-      <c r="G38" s="11"/>
+      <c r="G38" s="10"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
@@ -2199,16 +2196,16 @@
       <c r="C39" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D39" s="12">
+      <c r="D39" s="11">
         <v>36</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="13">
+      <c r="F39" s="12">
         <v>8</v>
       </c>
-      <c r="G39" s="11"/>
+      <c r="G39" s="10"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
@@ -2220,16 +2217,16 @@
       <c r="C40" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D40" s="12">
+      <c r="D40" s="11">
         <v>36</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F40" s="13">
+      <c r="F40" s="12">
         <v>10</v>
       </c>
-      <c r="G40" s="11"/>
+      <c r="G40" s="10"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
@@ -2241,16 +2238,16 @@
       <c r="C41" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D41" s="12">
+      <c r="D41" s="11">
         <v>65</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F41" s="13">
+      <c r="F41" s="12">
         <v>4</v>
       </c>
-      <c r="G41" s="11"/>
+      <c r="G41" s="10"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
@@ -2262,16 +2259,16 @@
       <c r="C42" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D42" s="12">
+      <c r="D42" s="11">
         <v>65</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F42" s="13">
+      <c r="F42" s="12">
         <v>3</v>
       </c>
-      <c r="G42" s="11"/>
+      <c r="G42" s="10"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
@@ -2283,16 +2280,16 @@
       <c r="C43" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D43" s="12">
+      <c r="D43" s="11">
         <v>65</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F43" s="13">
+      <c r="F43" s="12">
         <v>2</v>
       </c>
-      <c r="G43" s="11"/>
+      <c r="G43" s="10"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
@@ -2304,16 +2301,16 @@
       <c r="C44" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D44" s="12">
+      <c r="D44" s="11">
         <v>145</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F44" s="13">
+      <c r="F44" s="12">
         <v>5</v>
       </c>
-      <c r="G44" s="11"/>
+      <c r="G44" s="10"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
@@ -2325,16 +2322,16 @@
       <c r="C45" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D45" s="12">
+      <c r="D45" s="11">
         <v>145</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F45" s="13">
+      <c r="F45" s="12">
         <v>0</v>
       </c>
-      <c r="G45" s="11"/>
+      <c r="G45" s="10"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
@@ -2346,16 +2343,16 @@
       <c r="C46" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D46" s="12">
+      <c r="D46" s="11">
         <v>145</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F46" s="13">
-        <v>3</v>
-      </c>
-      <c r="G46" s="11"/>
+      <c r="F46" s="12">
+        <v>2</v>
+      </c>
+      <c r="G46" s="10"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
@@ -2367,16 +2364,16 @@
       <c r="C47" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D47" s="12">
+      <c r="D47" s="11">
         <v>29.8</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F47" s="13">
+      <c r="F47" s="12">
         <v>0</v>
       </c>
-      <c r="G47" s="11"/>
+      <c r="G47" s="10"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
@@ -2388,16 +2385,16 @@
       <c r="C48" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D48" s="12">
+      <c r="D48" s="11">
         <v>29.8</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F48" s="13">
+      <c r="F48" s="12">
         <v>0</v>
       </c>
-      <c r="G48" s="11"/>
+      <c r="G48" s="10"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
@@ -2409,16 +2406,16 @@
       <c r="C49" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D49" s="12">
+      <c r="D49" s="11">
         <v>29.8</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F49" s="13">
+      <c r="F49" s="12">
         <v>0</v>
       </c>
-      <c r="G49" s="11"/>
+      <c r="G49" s="10"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
@@ -2430,16 +2427,16 @@
       <c r="C50" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D50" s="12">
+      <c r="D50" s="11">
         <v>69.150000000000006</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F50" s="13">
+      <c r="F50" s="12">
         <v>0</v>
       </c>
-      <c r="G50" s="11"/>
+      <c r="G50" s="10"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
@@ -2451,16 +2448,16 @@
       <c r="C51" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D51" s="12">
+      <c r="D51" s="11">
         <v>69.150000000000006</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F51" s="13">
+      <c r="F51" s="12">
         <v>0</v>
       </c>
-      <c r="G51" s="11"/>
+      <c r="G51" s="10"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
@@ -2472,16 +2469,16 @@
       <c r="C52" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D52" s="12">
+      <c r="D52" s="11">
         <v>69.150000000000006</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F52" s="13">
+      <c r="F52" s="12">
         <v>0</v>
       </c>
-      <c r="G52" s="11"/>
+      <c r="G52" s="10"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
@@ -2493,16 +2490,16 @@
       <c r="C53" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D53" s="12">
+      <c r="D53" s="11">
         <v>150.49</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F53" s="13">
+      <c r="F53" s="12">
         <v>0</v>
       </c>
-      <c r="G53" s="11"/>
+      <c r="G53" s="10"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
@@ -2514,16 +2511,16 @@
       <c r="C54" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D54" s="12">
+      <c r="D54" s="11">
         <v>150.49</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F54" s="13">
+      <c r="F54" s="12">
         <v>0</v>
       </c>
-      <c r="G54" s="11"/>
+      <c r="G54" s="10"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
@@ -2535,16 +2532,16 @@
       <c r="C55" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D55" s="12">
+      <c r="D55" s="11">
         <v>150.49</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="F55" s="13">
+      <c r="F55" s="12">
         <v>-2</v>
       </c>
-      <c r="G55" s="11"/>
+      <c r="G55" s="10"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
@@ -2556,16 +2553,16 @@
       <c r="C56" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D56" s="12">
+      <c r="D56" s="11">
         <v>35</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="F56" s="13">
+      <c r="F56" s="12">
         <v>5</v>
       </c>
-      <c r="G56" s="11"/>
+      <c r="G56" s="10"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
@@ -2577,16 +2574,16 @@
       <c r="C57" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D57" s="12">
+      <c r="D57" s="11">
         <v>35</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="F57" s="13">
+      <c r="F57" s="12">
         <v>5</v>
       </c>
-      <c r="G57" s="11"/>
+      <c r="G57" s="10"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
@@ -2598,16 +2595,16 @@
       <c r="C58" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D58" s="12">
+      <c r="D58" s="11">
         <v>35</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F58" s="13">
+      <c r="F58" s="12">
         <v>5</v>
       </c>
-      <c r="G58" s="11"/>
+      <c r="G58" s="10"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
@@ -2619,16 +2616,16 @@
       <c r="C59" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D59" s="12">
+      <c r="D59" s="11">
         <v>151</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F59" s="13">
+      <c r="F59" s="12">
         <v>2</v>
       </c>
-      <c r="G59" s="11"/>
+      <c r="G59" s="10"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
@@ -2640,16 +2637,16 @@
       <c r="C60" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D60" s="12">
+      <c r="D60" s="11">
         <v>151</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F60" s="13">
+      <c r="F60" s="12">
         <v>0</v>
       </c>
-      <c r="G60" s="11"/>
+      <c r="G60" s="10"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
@@ -2661,16 +2658,16 @@
       <c r="C61" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D61" s="12">
+      <c r="D61" s="11">
         <v>151</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F61" s="13">
+      <c r="F61" s="12">
         <v>3</v>
       </c>
-      <c r="G61" s="11"/>
+      <c r="G61" s="10"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
@@ -2682,16 +2679,16 @@
       <c r="C62" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D62" s="12">
+      <c r="D62" s="11">
         <v>37</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F62" s="13">
+      <c r="F62" s="12">
         <v>5</v>
       </c>
-      <c r="G62" s="11"/>
+      <c r="G62" s="10"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
@@ -2703,16 +2700,16 @@
       <c r="C63" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D63" s="12">
+      <c r="D63" s="11">
         <v>37</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="F63" s="13">
+      <c r="F63" s="12">
         <v>6</v>
       </c>
-      <c r="G63" s="11"/>
+      <c r="G63" s="10"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
@@ -2724,16 +2721,16 @@
       <c r="C64" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D64" s="12">
+      <c r="D64" s="11">
         <v>37</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="F64" s="13">
+      <c r="F64" s="12">
         <v>0</v>
       </c>
-      <c r="G64" s="11"/>
+      <c r="G64" s="10"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
@@ -2745,16 +2742,16 @@
       <c r="C65" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D65" s="12">
+      <c r="D65" s="11">
         <v>42.300000000000004</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="F65" s="13">
+      <c r="F65" s="12">
         <v>0</v>
       </c>
-      <c r="G65" s="11"/>
+      <c r="G65" s="10"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
@@ -2766,16 +2763,16 @@
       <c r="C66" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D66" s="12">
+      <c r="D66" s="11">
         <v>42.300000000000004</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="F66" s="13">
+      <c r="F66" s="12">
         <v>3</v>
       </c>
-      <c r="G66" s="11"/>
+      <c r="G66" s="10"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
@@ -2787,16 +2784,16 @@
       <c r="C67" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D67" s="12">
+      <c r="D67" s="11">
         <v>42.300000000000004</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="F67" s="13">
+      <c r="F67" s="12">
         <v>3</v>
       </c>
-      <c r="G67" s="11"/>
+      <c r="G67" s="10"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
@@ -2808,16 +2805,16 @@
       <c r="C68" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D68" s="12">
+      <c r="D68" s="11">
         <v>109.49000000000001</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="F68" s="13">
+      <c r="F68" s="12">
         <v>1</v>
       </c>
-      <c r="G68" s="11"/>
+      <c r="G68" s="10"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
@@ -2829,16 +2826,16 @@
       <c r="C69" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D69" s="12">
+      <c r="D69" s="11">
         <v>96.850000000000009</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="F69" s="13">
+      <c r="F69" s="12">
         <v>2</v>
       </c>
-      <c r="G69" s="11"/>
+      <c r="G69" s="10"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
@@ -2850,16 +2847,16 @@
       <c r="C70" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D70" s="12">
+      <c r="D70" s="11">
         <v>96.850000000000009</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="F70" s="13">
+      <c r="F70" s="12">
         <v>2</v>
       </c>
-      <c r="G70" s="11"/>
+      <c r="G70" s="10"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
@@ -2871,16 +2868,16 @@
       <c r="C71" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D71" s="12">
+      <c r="D71" s="11">
         <v>37</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="F71" s="13">
+      <c r="F71" s="12">
         <v>-1</v>
       </c>
-      <c r="G71" s="11"/>
+      <c r="G71" s="10"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
@@ -2892,16 +2889,16 @@
       <c r="C72" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D72" s="12">
+      <c r="D72" s="11">
         <v>34</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="F72" s="13">
+      <c r="F72" s="12">
         <v>1</v>
       </c>
-      <c r="G72" s="11"/>
+      <c r="G72" s="10"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
@@ -2913,16 +2910,16 @@
       <c r="C73" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D73" s="12">
+      <c r="D73" s="11">
         <v>34</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="F73" s="13">
-        <v>3</v>
-      </c>
-      <c r="G73" s="11"/>
+      <c r="F73" s="12">
+        <v>2</v>
+      </c>
+      <c r="G73" s="10"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
@@ -2934,16 +2931,16 @@
       <c r="C74" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D74" s="12">
+      <c r="D74" s="11">
         <v>46.5</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F74" s="13">
+      <c r="F74" s="12">
         <v>2</v>
       </c>
-      <c r="G74" s="11"/>
+      <c r="G74" s="10"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
@@ -2955,16 +2952,16 @@
       <c r="C75" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D75" s="12">
+      <c r="D75" s="11">
         <v>60</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="F75" s="13">
+      <c r="F75" s="12">
         <v>1</v>
       </c>
-      <c r="G75" s="11"/>
+      <c r="G75" s="10"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
@@ -2976,16 +2973,16 @@
       <c r="C76" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D76" s="12">
+      <c r="D76" s="11">
         <v>60</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="F76" s="13">
+      <c r="F76" s="12">
         <v>7</v>
       </c>
-      <c r="G76" s="11"/>
+      <c r="G76" s="10"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
@@ -2997,16 +2994,16 @@
       <c r="C77" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D77" s="12">
+      <c r="D77" s="11">
         <v>136</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="F77" s="13">
+      <c r="F77" s="12">
         <v>1</v>
       </c>
-      <c r="G77" s="11"/>
+      <c r="G77" s="10"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
@@ -3018,16 +3015,16 @@
       <c r="C78" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D78" s="12">
+      <c r="D78" s="11">
         <v>136</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F78" s="13">
+      <c r="F78" s="12">
         <v>2</v>
       </c>
-      <c r="G78" s="11"/>
+      <c r="G78" s="10"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
@@ -3039,16 +3036,16 @@
       <c r="C79" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D79" s="12">
+      <c r="D79" s="11">
         <v>136</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="F79" s="13">
+      <c r="F79" s="12">
         <v>-1</v>
       </c>
-      <c r="G79" s="11"/>
+      <c r="G79" s="10"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
@@ -3060,16 +3057,16 @@
       <c r="C80" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D80" s="12">
+      <c r="D80" s="11">
         <v>53</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="F80" s="13">
+      <c r="F80" s="12">
         <v>4</v>
       </c>
-      <c r="G80" s="11"/>
+      <c r="G80" s="10"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
@@ -3081,16 +3078,16 @@
       <c r="C81" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D81" s="12">
+      <c r="D81" s="11">
         <v>53</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="F81" s="13">
+      <c r="F81" s="12">
         <v>1</v>
       </c>
-      <c r="G81" s="11"/>
+      <c r="G81" s="10"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
@@ -3102,16 +3099,16 @@
       <c r="C82" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D82" s="12">
+      <c r="D82" s="11">
         <v>123</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="F82" s="13">
+      <c r="F82" s="12">
         <v>3</v>
       </c>
-      <c r="G82" s="11"/>
+      <c r="G82" s="10"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
@@ -3123,16 +3120,16 @@
       <c r="C83" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D83" s="12">
+      <c r="D83" s="11">
         <v>123</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="F83" s="13">
+      <c r="F83" s="12">
         <v>3</v>
       </c>
-      <c r="G83" s="11"/>
+      <c r="G83" s="10"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B84" s="9" t="s">
@@ -3141,16 +3138,16 @@
       <c r="C84" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="D84" s="12">
+      <c r="D84" s="11">
         <v>36</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="F84" s="13">
+      <c r="F84" s="12">
         <v>3</v>
       </c>
-      <c r="G84" s="11"/>
+      <c r="G84" s="10"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B85" s="9" t="s">
@@ -3159,16 +3156,16 @@
       <c r="C85" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D85" s="12">
+      <c r="D85" s="11">
         <v>107</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="F85" s="13">
+      <c r="F85" s="12">
         <v>3</v>
       </c>
-      <c r="G85" s="11"/>
+      <c r="G85" s="10"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
@@ -3180,16 +3177,16 @@
       <c r="C86" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D86" s="12">
+      <c r="D86" s="11">
         <v>39.5</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="F86" s="13">
+      <c r="F86" s="12">
         <v>2</v>
       </c>
-      <c r="G86" s="11"/>
+      <c r="G86" s="10"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
@@ -3201,16 +3198,16 @@
       <c r="C87" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D87" s="12">
+      <c r="D87" s="11">
         <v>39.5</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="F87" s="13">
+      <c r="F87" s="12">
         <v>2</v>
       </c>
-      <c r="G87" s="11"/>
+      <c r="G87" s="10"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
@@ -3222,16 +3219,16 @@
       <c r="C88" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D88" s="12">
+      <c r="D88" s="11">
         <v>90</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="F88" s="13">
+      <c r="F88" s="12">
         <v>2</v>
       </c>
-      <c r="G88" s="11"/>
+      <c r="G88" s="10"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
@@ -3243,16 +3240,16 @@
       <c r="C89" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D89" s="12">
+      <c r="D89" s="11">
         <v>86</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="F89" s="13">
+      <c r="F89" s="12">
         <v>3</v>
       </c>
-      <c r="G89" s="11"/>
+      <c r="G89" s="10"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
@@ -3264,16 +3261,16 @@
       <c r="C90" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D90" s="12">
+      <c r="D90" s="11">
         <v>130</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="F90" s="13">
+      <c r="F90" s="12">
         <v>1</v>
       </c>
-      <c r="G90" s="11"/>
+      <c r="G90" s="10"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
@@ -3285,16 +3282,16 @@
       <c r="C91" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D91" s="12">
+      <c r="D91" s="11">
         <v>130</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="F91" s="13">
+      <c r="F91" s="12">
         <v>2</v>
       </c>
-      <c r="G91" s="11"/>
+      <c r="G91" s="10"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B92" s="9" t="s">
@@ -3303,16 +3300,16 @@
       <c r="C92" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D92" s="12">
+      <c r="D92" s="11">
         <v>34.5</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="F92" s="13">
-        <v>3</v>
-      </c>
-      <c r="G92" s="11"/>
+      <c r="F92" s="12">
+        <v>1</v>
+      </c>
+      <c r="G92" s="10"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B93" s="9" t="s">
@@ -3321,16 +3318,16 @@
       <c r="C93" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D93" s="12">
+      <c r="D93" s="11">
         <v>71.5</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F93" s="13">
+      <c r="F93" s="12">
         <v>0</v>
       </c>
-      <c r="G93" s="11"/>
+      <c r="G93" s="10"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B94" s="9" t="s">
@@ -3339,16 +3336,16 @@
       <c r="C94" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D94" s="12">
+      <c r="D94" s="11">
         <v>131.5</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="F94" s="13">
+      <c r="F94" s="12">
         <v>0</v>
       </c>
-      <c r="G94" s="11"/>
+      <c r="G94" s="10"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
@@ -3360,16 +3357,16 @@
       <c r="C95" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D95" s="12">
+      <c r="D95" s="11">
         <v>36</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="F95" s="13">
+      <c r="F95" s="12">
         <v>3</v>
       </c>
-      <c r="G95" s="11"/>
+      <c r="G95" s="10"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
@@ -3381,16 +3378,16 @@
       <c r="C96" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D96" s="12">
+      <c r="D96" s="11">
         <v>36</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="F96" s="13">
+      <c r="F96" s="12">
         <v>1</v>
       </c>
-      <c r="G96" s="11"/>
+      <c r="G96" s="10"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
@@ -3402,16 +3399,16 @@
       <c r="C97" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D97" s="12">
+      <c r="D97" s="11">
         <v>78</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="F97" s="13">
+      <c r="F97" s="12">
         <v>3</v>
       </c>
-      <c r="G97" s="11"/>
+      <c r="G97" s="10"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
@@ -3423,16 +3420,16 @@
       <c r="C98" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D98" s="12">
+      <c r="D98" s="11">
         <v>78</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="F98" s="13">
+      <c r="F98" s="12">
         <v>2</v>
       </c>
-      <c r="G98" s="11"/>
+      <c r="G98" s="10"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
@@ -3444,16 +3441,16 @@
       <c r="C99" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D99" s="12">
+      <c r="D99" s="11">
         <v>150</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="F99" s="13">
+      <c r="F99" s="12">
         <v>2</v>
       </c>
-      <c r="G99" s="11"/>
+      <c r="G99" s="10"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
@@ -3465,16 +3462,16 @@
       <c r="C100" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D100" s="12">
+      <c r="D100" s="11">
         <v>150</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="F100" s="13">
+      <c r="F100" s="12">
         <v>2</v>
       </c>
-      <c r="G100" s="11"/>
+      <c r="G100" s="10"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B101" s="9" t="s">
@@ -3483,16 +3480,16 @@
       <c r="C101" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D101" s="12">
+      <c r="D101" s="11">
         <v>55</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="F101" s="13">
+      <c r="F101" s="12">
         <v>0</v>
       </c>
-      <c r="G101" s="11"/>
+      <c r="G101" s="10"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
@@ -3504,16 +3501,16 @@
       <c r="C102" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D102" s="12">
+      <c r="D102" s="11">
         <v>35.5</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="F102" s="13">
+      <c r="F102" s="12">
         <v>6</v>
       </c>
-      <c r="G102" s="11"/>
+      <c r="G102" s="10"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
@@ -3525,16 +3522,16 @@
       <c r="C103" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D103" s="12">
+      <c r="D103" s="11">
         <v>35.5</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="F103" s="13">
+      <c r="F103" s="12">
         <v>0</v>
       </c>
-      <c r="G103" s="11"/>
+      <c r="G103" s="10"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
@@ -3546,16 +3543,16 @@
       <c r="C104" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D104" s="12">
+      <c r="D104" s="11">
         <v>35.5</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="F104" s="13">
+      <c r="F104" s="12">
         <v>4</v>
       </c>
-      <c r="G104" s="11"/>
+      <c r="G104" s="10"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
@@ -3567,16 +3564,16 @@
       <c r="C105" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D105" s="12">
+      <c r="D105" s="11">
         <v>53.95</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="F105" s="13">
+      <c r="F105" s="12">
         <v>0</v>
       </c>
-      <c r="G105" s="11"/>
+      <c r="G105" s="10"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
@@ -3588,16 +3585,16 @@
       <c r="C106" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D106" s="12">
-        <v>59</v>
+      <c r="D106" s="11">
+        <v>64</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="F106" s="13">
-        <v>5</v>
-      </c>
-      <c r="G106" s="11"/>
+      <c r="F106" s="12">
+        <v>8</v>
+      </c>
+      <c r="G106" s="10"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
@@ -3609,16 +3606,16 @@
       <c r="C107" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D107" s="12">
+      <c r="D107" s="11">
         <v>53.95</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F107" s="13">
-        <v>4</v>
-      </c>
-      <c r="G107" s="11"/>
+      <c r="F107" s="12">
+        <v>3</v>
+      </c>
+      <c r="G107" s="10"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
@@ -3630,16 +3627,16 @@
       <c r="C108" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D108" s="12">
+      <c r="D108" s="11">
         <v>146</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="F108" s="13">
+      <c r="F108" s="12">
         <v>0</v>
       </c>
-      <c r="G108" s="11"/>
+      <c r="G108" s="10"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
@@ -3651,16 +3648,16 @@
       <c r="C109" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D109" s="12">
+      <c r="D109" s="11">
         <v>146</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="F109" s="13">
-        <v>3</v>
-      </c>
-      <c r="G109" s="11"/>
+      <c r="F109" s="12">
+        <v>2</v>
+      </c>
+      <c r="G109" s="10"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
@@ -3672,16 +3669,16 @@
       <c r="C110" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D110" s="12">
+      <c r="D110" s="11">
         <v>146</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="F110" s="13">
+      <c r="F110" s="12">
         <v>1</v>
       </c>
-      <c r="G110" s="11"/>
+      <c r="G110" s="10"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
@@ -3693,16 +3690,16 @@
       <c r="C111" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D111" s="12">
+      <c r="D111" s="11">
         <v>20.5</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="F111" s="13">
+      <c r="F111" s="12">
         <v>4</v>
       </c>
-      <c r="G111" s="11"/>
+      <c r="G111" s="10"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
@@ -3714,16 +3711,16 @@
       <c r="C112" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D112" s="12">
+      <c r="D112" s="11">
         <v>34.15</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="F112" s="13">
+      <c r="F112" s="12">
         <v>1</v>
       </c>
-      <c r="G112" s="11"/>
+      <c r="G112" s="10"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
@@ -3735,16 +3732,16 @@
       <c r="C113" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D113" s="12">
+      <c r="D113" s="11">
         <v>34.15</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="F113" s="13">
+      <c r="F113" s="12">
         <v>1</v>
       </c>
-      <c r="G113" s="11"/>
+      <c r="G113" s="10"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
@@ -3756,31 +3753,31 @@
       <c r="C114" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D114" s="12">
+      <c r="D114" s="11">
         <v>76.350000000000009</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="F114" s="13">
+      <c r="F114" s="12">
         <v>2</v>
       </c>
-      <c r="G114" s="11"/>
+      <c r="G114" s="10"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B115" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="D115" s="12">
+      <c r="D115" s="11">
         <v>6.55</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F115" s="13">
+      <c r="F115" s="12">
         <v>0</v>
       </c>
-      <c r="G115" s="11"/>
+      <c r="G115" s="10"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B116" s="9" t="s">
@@ -3789,16 +3786,16 @@
       <c r="C116" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D116" s="12">
-        <v>8.5</v>
+      <c r="D116" s="11">
+        <v>10</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="F116" s="13">
-        <v>2</v>
-      </c>
-      <c r="G116" s="11"/>
+      <c r="F116" s="12">
+        <v>8</v>
+      </c>
+      <c r="G116" s="10"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B117" s="9" t="s">
@@ -3807,16 +3804,16 @@
       <c r="C117" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D117" s="12">
+      <c r="D117" s="11">
         <v>8.5</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F117" s="13">
+      <c r="F117" s="12">
         <v>1</v>
       </c>
-      <c r="G117" s="11"/>
+      <c r="G117" s="10"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B118" s="9" t="s">
@@ -3825,16 +3822,16 @@
       <c r="C118" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D118" s="12">
-        <v>8.5</v>
+      <c r="D118" s="11">
+        <v>10</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="F118" s="13">
+      <c r="F118" s="12">
         <v>2</v>
       </c>
-      <c r="G118" s="11"/>
+      <c r="G118" s="10"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
@@ -3846,16 +3843,16 @@
       <c r="C119" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D119" s="12">
+      <c r="D119" s="11">
         <v>46.35</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="F119" s="13">
+      <c r="F119" s="12">
         <v>3</v>
       </c>
-      <c r="G119" s="11"/>
+      <c r="G119" s="10"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
@@ -3867,16 +3864,16 @@
       <c r="C120" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D120" s="12">
+      <c r="D120" s="11">
         <v>46.35</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="F120" s="13">
+      <c r="F120" s="12">
         <v>2</v>
       </c>
-      <c r="G120" s="11"/>
+      <c r="G120" s="10"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
@@ -3888,16 +3885,16 @@
       <c r="C121" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D121" s="12">
+      <c r="D121" s="11">
         <v>107.35000000000001</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F121" s="13">
+      <c r="F121" s="12">
         <v>2</v>
       </c>
-      <c r="G121" s="11"/>
+      <c r="G121" s="10"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
@@ -3909,16 +3906,16 @@
       <c r="C122" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D122" s="12">
+      <c r="D122" s="11">
         <v>52</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="F122" s="13">
+      <c r="F122" s="12">
         <v>2</v>
       </c>
-      <c r="G122" s="11"/>
+      <c r="G122" s="10"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
@@ -3930,16 +3927,16 @@
       <c r="C123" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D123" s="12">
+      <c r="D123" s="11">
         <v>52</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="F123" s="13">
+      <c r="F123" s="12">
         <v>0</v>
       </c>
-      <c r="G123" s="11"/>
+      <c r="G123" s="10"/>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
@@ -3951,16 +3948,16 @@
       <c r="C124" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D124" s="12">
-        <v>52</v>
+      <c r="D124" s="11">
+        <v>55</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="F124" s="13">
-        <v>1</v>
-      </c>
-      <c r="G124" s="11"/>
+      <c r="F124" s="12">
+        <v>4</v>
+      </c>
+      <c r="G124" s="10"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
@@ -3972,16 +3969,16 @@
       <c r="C125" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D125" s="12">
+      <c r="D125" s="11">
         <v>95.990000000000009</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="F125" s="13">
+      <c r="F125" s="12">
         <v>3</v>
       </c>
-      <c r="G125" s="11"/>
+      <c r="G125" s="10"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
@@ -3993,16 +3990,16 @@
       <c r="C126" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D126" s="12">
+      <c r="D126" s="11">
         <v>114.49000000000001</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="F126" s="13">
+      <c r="F126" s="12">
         <v>2</v>
       </c>
-      <c r="G126" s="11"/>
+      <c r="G126" s="10"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
@@ -4014,16 +4011,16 @@
       <c r="C127" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D127" s="12">
+      <c r="D127" s="11">
         <v>95.990000000000009</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="F127" s="13">
+      <c r="F127" s="12">
         <v>1</v>
       </c>
-      <c r="G127" s="11"/>
+      <c r="G127" s="10"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
@@ -4035,16 +4032,16 @@
       <c r="C128" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D128" s="12">
+      <c r="D128" s="11">
         <v>212</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="F128" s="13">
+      <c r="F128" s="12">
         <v>2</v>
       </c>
-      <c r="G128" s="11"/>
+      <c r="G128" s="10"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
@@ -4056,16 +4053,16 @@
       <c r="C129" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D129" s="12">
+      <c r="D129" s="11">
         <v>212</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="F129" s="13">
+      <c r="F129" s="12">
         <v>3</v>
       </c>
-      <c r="G129" s="11"/>
+      <c r="G129" s="10"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
@@ -4077,16 +4074,16 @@
       <c r="C130" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D130" s="12">
+      <c r="D130" s="11">
         <v>212</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="F130" s="13">
+      <c r="F130" s="12">
         <v>0</v>
       </c>
-      <c r="G130" s="11"/>
+      <c r="G130" s="10"/>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B131" s="9" t="s">
@@ -4095,16 +4092,16 @@
       <c r="C131" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D131" s="12">
+      <c r="D131" s="11">
         <v>40</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="F131" s="13">
+      <c r="F131" s="12">
         <v>2</v>
       </c>
-      <c r="G131" s="11"/>
+      <c r="G131" s="10"/>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B132" s="9" t="s">
@@ -4113,16 +4110,16 @@
       <c r="C132" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D132" s="12">
+      <c r="D132" s="11">
         <v>86</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="F132" s="13">
+      <c r="F132" s="12">
         <v>0</v>
       </c>
-      <c r="G132" s="11"/>
+      <c r="G132" s="10"/>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B133" s="9" t="s">
@@ -4131,16 +4128,16 @@
       <c r="C133" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D133" s="12">
+      <c r="D133" s="11">
         <v>108.31</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="F133" s="13">
+      <c r="F133" s="12">
         <v>1</v>
       </c>
-      <c r="G133" s="11"/>
+      <c r="G133" s="10"/>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B134" s="9" t="s">
@@ -4149,16 +4146,16 @@
       <c r="C134" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D134" s="12">
+      <c r="D134" s="11">
         <v>73.650000000000006</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F134" s="13">
+      <c r="F134" s="12">
         <v>2</v>
       </c>
-      <c r="G134" s="11"/>
+      <c r="G134" s="10"/>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B135" s="9" t="s">
@@ -4167,16 +4164,16 @@
       <c r="C135" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D135" s="12">
+      <c r="D135" s="11">
         <v>190</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="F135" s="13">
+      <c r="F135" s="12">
         <v>1</v>
       </c>
-      <c r="G135" s="11"/>
+      <c r="G135" s="10"/>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B136" s="9" t="s">
@@ -4185,16 +4182,16 @@
       <c r="C136" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D136" s="12">
+      <c r="D136" s="11">
         <v>67</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="F136" s="13">
+      <c r="F136" s="12">
         <v>1</v>
       </c>
-      <c r="G136" s="11"/>
+      <c r="G136" s="10"/>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E137" s="2"/>

--- a/prix/levis.xlsx
+++ b/prix/levis.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358CFD79-8914-4F49-BEED-61F94E96744B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F97A5AC-91B7-4767-8AD5-1FBD98AF72EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="303">
   <si>
     <t>31100072</t>
   </si>
@@ -651,12 +651,6 @@
   </si>
   <si>
     <t>Lak rapide exter.base W 1/2l</t>
-  </si>
-  <si>
-    <t>31100325</t>
-  </si>
-  <si>
-    <t>Lak rapide exter.base M 1l</t>
   </si>
   <si>
     <t>31100326</t>
@@ -1009,7 +1003,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1035,6 +1029,9 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1379,7 +1376,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{065E4AF0-A4F8-4CE3-9E23-EDCEACB756BD}">
-  <dimension ref="A1:G444"/>
+  <dimension ref="A1:G443"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
@@ -1393,2751 +1390,2748 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="G1" s="2"/>
+      <c r="G1" s="11"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D2" s="11">
+        <v>273</v>
+      </c>
+      <c r="D2" s="12">
         <v>45</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="13">
         <v>7</v>
       </c>
-      <c r="G2" s="10"/>
+      <c r="G2" s="11"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D3" s="11">
+        <v>273</v>
+      </c>
+      <c r="D3" s="12">
         <v>45</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="12">
-        <v>8</v>
-      </c>
-      <c r="G3" s="10"/>
+      <c r="F3" s="13">
+        <v>7</v>
+      </c>
+      <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D4" s="11">
+        <v>276</v>
+      </c>
+      <c r="D4" s="12">
         <v>94</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="13">
         <v>6</v>
       </c>
-      <c r="G4" s="10"/>
+      <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D5" s="11">
+        <v>276</v>
+      </c>
+      <c r="D5" s="12">
         <v>94</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="12">
-        <v>4</v>
-      </c>
-      <c r="G5" s="10"/>
+      <c r="F5" s="13">
+        <v>3</v>
+      </c>
+      <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D6" s="11">
+        <v>275</v>
+      </c>
+      <c r="D6" s="12">
         <v>175</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="13">
         <v>6</v>
       </c>
-      <c r="G6" s="10"/>
+      <c r="G6" s="11"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D7" s="11">
+        <v>275</v>
+      </c>
+      <c r="D7" s="12">
         <v>175</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="13">
         <v>1</v>
       </c>
-      <c r="G7" s="10"/>
+      <c r="G7" s="11"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D8" s="11">
+        <v>275</v>
+      </c>
+      <c r="D8" s="12">
         <v>175</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="12">
-        <v>4</v>
-      </c>
-      <c r="G8" s="10"/>
+      <c r="F8" s="13">
+        <v>3</v>
+      </c>
+      <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D9" s="11">
+        <v>273</v>
+      </c>
+      <c r="D9" s="12">
         <v>47.25</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="13">
         <v>0</v>
       </c>
-      <c r="G9" s="10"/>
+      <c r="G9" s="11"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D10" s="11">
+        <v>273</v>
+      </c>
+      <c r="D10" s="12">
         <v>45</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="13">
         <v>3</v>
       </c>
-      <c r="G10" s="10"/>
+      <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D11" s="11">
+        <v>273</v>
+      </c>
+      <c r="D11" s="12">
         <v>45</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="13">
         <v>0</v>
       </c>
-      <c r="G11" s="10"/>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D12" s="11">
+        <v>273</v>
+      </c>
+      <c r="D12" s="12">
         <v>45</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="13">
         <v>4</v>
       </c>
-      <c r="G12" s="10"/>
+      <c r="G12" s="11"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>23</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D13" s="11">
+        <v>276</v>
+      </c>
+      <c r="D13" s="12">
         <v>94</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="13">
         <v>2</v>
       </c>
-      <c r="G13" s="10"/>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>25</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D14" s="11">
+        <v>276</v>
+      </c>
+      <c r="D14" s="12">
         <v>94</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="13">
         <v>0</v>
       </c>
-      <c r="G14" s="10"/>
+      <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D15" s="11">
+        <v>276</v>
+      </c>
+      <c r="D15" s="12">
         <v>94</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="13">
         <v>2</v>
       </c>
-      <c r="G15" s="10"/>
+      <c r="G15" s="11"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>29</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D16" s="11">
+        <v>275</v>
+      </c>
+      <c r="D16" s="12">
         <v>175</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="13">
         <v>3</v>
       </c>
-      <c r="G16" s="10"/>
+      <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D17" s="11">
+        <v>275</v>
+      </c>
+      <c r="D17" s="12">
         <v>175</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="13">
         <v>0</v>
       </c>
-      <c r="G17" s="10"/>
+      <c r="G17" s="11"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>33</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D18" s="11">
+        <v>275</v>
+      </c>
+      <c r="D18" s="12">
         <v>175</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="13">
         <v>6</v>
       </c>
-      <c r="G18" s="10"/>
+      <c r="G18" s="11"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B19" s="9" t="s">
         <v>35</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D19" s="11">
+        <v>273</v>
+      </c>
+      <c r="D19" s="12">
         <v>46.95</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="13">
         <v>0</v>
       </c>
-      <c r="G19" s="10"/>
+      <c r="G19" s="11"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>37</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D20" s="11">
+        <v>277</v>
+      </c>
+      <c r="D20" s="12">
         <v>32</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="13">
         <v>1</v>
       </c>
-      <c r="G20" s="10"/>
+      <c r="G20" s="11"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>39</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D21" s="11">
+        <v>277</v>
+      </c>
+      <c r="D21" s="12">
         <v>32</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="13">
         <v>3</v>
       </c>
-      <c r="G21" s="10"/>
+      <c r="G21" s="11"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D22" s="11">
+        <v>277</v>
+      </c>
+      <c r="D22" s="12">
         <v>32</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="13">
         <v>3</v>
       </c>
-      <c r="G22" s="10"/>
+      <c r="G22" s="11"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>43</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D23" s="11">
+        <v>273</v>
+      </c>
+      <c r="D23" s="12">
         <v>58</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F23" s="12">
+      <c r="F23" s="13">
         <v>0</v>
       </c>
-      <c r="G23" s="10"/>
+      <c r="G23" s="11"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>45</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D24" s="11">
+        <v>273</v>
+      </c>
+      <c r="D24" s="12">
         <v>58</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F24" s="13">
         <v>3</v>
       </c>
-      <c r="G24" s="10"/>
+      <c r="G24" s="11"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>47</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D25" s="11">
+        <v>273</v>
+      </c>
+      <c r="D25" s="12">
         <v>58</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F25" s="12">
+      <c r="F25" s="13">
         <v>2</v>
       </c>
-      <c r="G25" s="10"/>
+      <c r="G25" s="11"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>49</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D26" s="11">
-        <v>135.5</v>
+        <v>276</v>
+      </c>
+      <c r="D26" s="12">
+        <v>145</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F26" s="12">
-        <v>2</v>
-      </c>
-      <c r="G26" s="10"/>
+      <c r="F26" s="13">
+        <v>1</v>
+      </c>
+      <c r="G26" s="11"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D27" s="11">
+        <v>276</v>
+      </c>
+      <c r="D27" s="12">
         <v>135.5</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F27" s="12">
+      <c r="F27" s="13">
         <v>3</v>
       </c>
-      <c r="G27" s="10"/>
+      <c r="G27" s="11"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>53</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D28" s="11">
+        <v>276</v>
+      </c>
+      <c r="D28" s="12">
         <v>135.5</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="12">
+      <c r="F28" s="13">
         <v>7</v>
       </c>
-      <c r="G28" s="10"/>
+      <c r="G28" s="11"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>55</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D29" s="11">
-        <v>36</v>
+        <v>277</v>
+      </c>
+      <c r="D29" s="12">
+        <v>37</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F29" s="12">
-        <v>2</v>
-      </c>
-      <c r="G29" s="10"/>
+      <c r="F29" s="13">
+        <v>5</v>
+      </c>
+      <c r="G29" s="11"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>57</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D30" s="11">
+        <v>277</v>
+      </c>
+      <c r="D30" s="12">
         <v>36</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="12">
+      <c r="F30" s="13">
         <v>6</v>
       </c>
-      <c r="G30" s="10"/>
+      <c r="G30" s="11"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D31" s="11">
+        <v>277</v>
+      </c>
+      <c r="D31" s="12">
         <v>37</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F31" s="12">
+      <c r="F31" s="13">
         <v>12</v>
       </c>
-      <c r="G31" s="10"/>
+      <c r="G31" s="11"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>61</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D32" s="11">
+        <v>273</v>
+      </c>
+      <c r="D32" s="12">
         <v>65</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F32" s="12">
-        <v>2</v>
-      </c>
-      <c r="G32" s="10"/>
+      <c r="F32" s="13">
+        <v>11</v>
+      </c>
+      <c r="G32" s="11"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>63</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D33" s="11">
+        <v>273</v>
+      </c>
+      <c r="D33" s="12">
         <v>65</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F33" s="12">
+      <c r="F33" s="13">
         <v>1</v>
       </c>
-      <c r="G33" s="10"/>
+      <c r="G33" s="11"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>65</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D34" s="11">
+        <v>273</v>
+      </c>
+      <c r="D34" s="12">
         <v>65</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F34" s="12">
+      <c r="F34" s="13">
         <v>8</v>
       </c>
-      <c r="G34" s="10"/>
+      <c r="G34" s="11"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>67</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D35" s="11">
+        <v>276</v>
+      </c>
+      <c r="D35" s="12">
         <v>150</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F35" s="12">
-        <v>6</v>
-      </c>
-      <c r="G35" s="10"/>
+      <c r="F35" s="13">
+        <v>4</v>
+      </c>
+      <c r="G35" s="11"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>69</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D36" s="11">
+        <v>276</v>
+      </c>
+      <c r="D36" s="12">
         <v>150</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F36" s="12">
+      <c r="F36" s="13">
         <v>0</v>
       </c>
-      <c r="G36" s="10"/>
+      <c r="G36" s="11"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D37" s="11">
+        <v>276</v>
+      </c>
+      <c r="D37" s="12">
         <v>150</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F37" s="12">
-        <v>5</v>
-      </c>
-      <c r="G37" s="10"/>
+      <c r="F37" s="13">
+        <v>4</v>
+      </c>
+      <c r="G37" s="11"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>73</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D38" s="11">
+        <v>277</v>
+      </c>
+      <c r="D38" s="12">
         <v>36</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F38" s="12">
+      <c r="F38" s="13">
         <v>7</v>
       </c>
-      <c r="G38" s="10"/>
+      <c r="G38" s="11"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B39" s="9" t="s">
         <v>75</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D39" s="11">
+        <v>277</v>
+      </c>
+      <c r="D39" s="12">
         <v>36</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="12">
+      <c r="F39" s="13">
         <v>8</v>
       </c>
-      <c r="G39" s="10"/>
+      <c r="G39" s="11"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B40" s="9" t="s">
         <v>77</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D40" s="11">
+        <v>277</v>
+      </c>
+      <c r="D40" s="12">
         <v>36</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F40" s="12">
+      <c r="F40" s="13">
         <v>10</v>
       </c>
-      <c r="G40" s="10"/>
+      <c r="G40" s="11"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>79</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D41" s="11">
+        <v>273</v>
+      </c>
+      <c r="D41" s="12">
         <v>65</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F41" s="12">
+      <c r="F41" s="13">
         <v>4</v>
       </c>
-      <c r="G41" s="10"/>
+      <c r="G41" s="11"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B42" s="9" t="s">
         <v>81</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D42" s="11">
+        <v>273</v>
+      </c>
+      <c r="D42" s="12">
         <v>65</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F42" s="12">
+      <c r="F42" s="13">
         <v>3</v>
       </c>
-      <c r="G42" s="10"/>
+      <c r="G42" s="11"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B43" s="9" t="s">
         <v>83</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D43" s="11">
+        <v>273</v>
+      </c>
+      <c r="D43" s="12">
         <v>65</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F43" s="12">
+      <c r="F43" s="13">
         <v>2</v>
       </c>
-      <c r="G43" s="10"/>
+      <c r="G43" s="11"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B44" s="9" t="s">
         <v>85</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D44" s="11">
+        <v>276</v>
+      </c>
+      <c r="D44" s="12">
         <v>145</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F44" s="12">
+      <c r="F44" s="13">
         <v>5</v>
       </c>
-      <c r="G44" s="10"/>
+      <c r="G44" s="11"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B45" s="9" t="s">
         <v>87</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D45" s="11">
+        <v>276</v>
+      </c>
+      <c r="D45" s="12">
         <v>145</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F45" s="12">
+      <c r="F45" s="13">
         <v>0</v>
       </c>
-      <c r="G45" s="10"/>
+      <c r="G45" s="11"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B46" s="9" t="s">
         <v>89</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D46" s="11">
+        <v>276</v>
+      </c>
+      <c r="D46" s="12">
         <v>145</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F46" s="12">
-        <v>2</v>
-      </c>
-      <c r="G46" s="10"/>
+      <c r="F46" s="13">
+        <v>1</v>
+      </c>
+      <c r="G46" s="11"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B47" s="9" t="s">
         <v>91</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D47" s="11">
+        <v>273</v>
+      </c>
+      <c r="D47" s="12">
         <v>29.8</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F47" s="12">
+      <c r="F47" s="13">
         <v>0</v>
       </c>
-      <c r="G47" s="10"/>
+      <c r="G47" s="11"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B48" s="9" t="s">
         <v>93</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D48" s="11">
+        <v>273</v>
+      </c>
+      <c r="D48" s="12">
         <v>29.8</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F48" s="12">
+      <c r="F48" s="13">
         <v>0</v>
       </c>
-      <c r="G48" s="10"/>
+      <c r="G48" s="11"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B49" s="9" t="s">
         <v>95</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D49" s="11">
+        <v>273</v>
+      </c>
+      <c r="D49" s="12">
         <v>29.8</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F49" s="12">
+      <c r="F49" s="13">
         <v>0</v>
       </c>
-      <c r="G49" s="10"/>
+      <c r="G49" s="11"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B50" s="9" t="s">
         <v>97</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D50" s="11">
+        <v>276</v>
+      </c>
+      <c r="D50" s="12">
         <v>69.150000000000006</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F50" s="12">
+      <c r="F50" s="13">
         <v>0</v>
       </c>
-      <c r="G50" s="10"/>
+      <c r="G50" s="11"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B51" s="9" t="s">
         <v>99</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D51" s="11">
+        <v>276</v>
+      </c>
+      <c r="D51" s="12">
         <v>69.150000000000006</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F51" s="12">
+      <c r="F51" s="13">
         <v>0</v>
       </c>
-      <c r="G51" s="10"/>
+      <c r="G51" s="11"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B52" s="9" t="s">
         <v>101</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D52" s="11">
+        <v>276</v>
+      </c>
+      <c r="D52" s="12">
         <v>69.150000000000006</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F52" s="12">
+      <c r="F52" s="13">
         <v>0</v>
       </c>
-      <c r="G52" s="10"/>
+      <c r="G52" s="11"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>103</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D53" s="11">
+        <v>279</v>
+      </c>
+      <c r="D53" s="12">
         <v>150.49</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F53" s="12">
+      <c r="F53" s="13">
         <v>0</v>
       </c>
-      <c r="G53" s="10"/>
+      <c r="G53" s="11"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B54" s="9" t="s">
         <v>105</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D54" s="11">
+        <v>279</v>
+      </c>
+      <c r="D54" s="12">
         <v>150.49</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F54" s="12">
+      <c r="F54" s="13">
         <v>0</v>
       </c>
-      <c r="G54" s="10"/>
+      <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>107</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D55" s="11">
+        <v>279</v>
+      </c>
+      <c r="D55" s="12">
         <v>150.49</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="F55" s="12">
+      <c r="F55" s="13">
         <v>-2</v>
       </c>
-      <c r="G55" s="10"/>
+      <c r="G55" s="11"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B56" s="9" t="s">
         <v>109</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D56" s="11">
+        <v>277</v>
+      </c>
+      <c r="D56" s="12">
         <v>35</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="F56" s="12">
-        <v>5</v>
-      </c>
-      <c r="G56" s="10"/>
+      <c r="F56" s="13">
+        <v>4</v>
+      </c>
+      <c r="G56" s="11"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B57" s="9" t="s">
         <v>111</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D57" s="11">
+        <v>277</v>
+      </c>
+      <c r="D57" s="12">
         <v>35</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="F57" s="12">
+      <c r="F57" s="13">
         <v>5</v>
       </c>
-      <c r="G57" s="10"/>
+      <c r="G57" s="11"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B58" s="9" t="s">
         <v>113</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D58" s="11">
+        <v>277</v>
+      </c>
+      <c r="D58" s="12">
         <v>35</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F58" s="12">
+      <c r="F58" s="13">
         <v>5</v>
       </c>
-      <c r="G58" s="10"/>
+      <c r="G58" s="11"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B59" s="9" t="s">
         <v>115</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D59" s="11">
+        <v>276</v>
+      </c>
+      <c r="D59" s="12">
         <v>151</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F59" s="12">
+      <c r="F59" s="13">
         <v>2</v>
       </c>
-      <c r="G59" s="10"/>
+      <c r="G59" s="11"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B60" s="9" t="s">
         <v>117</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D60" s="11">
+        <v>276</v>
+      </c>
+      <c r="D60" s="12">
         <v>151</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F60" s="12">
+      <c r="F60" s="13">
         <v>0</v>
       </c>
-      <c r="G60" s="10"/>
+      <c r="G60" s="11"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B61" s="9" t="s">
         <v>119</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D61" s="11">
+        <v>276</v>
+      </c>
+      <c r="D61" s="12">
         <v>151</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F61" s="12">
+      <c r="F61" s="13">
         <v>3</v>
       </c>
-      <c r="G61" s="10"/>
+      <c r="G61" s="11"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B62" s="9" t="s">
         <v>121</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D62" s="11">
+        <v>277</v>
+      </c>
+      <c r="D62" s="12">
         <v>37</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F62" s="12">
+      <c r="F62" s="13">
         <v>5</v>
       </c>
-      <c r="G62" s="10"/>
+      <c r="G62" s="11"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B63" s="9" t="s">
         <v>123</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D63" s="11">
+        <v>277</v>
+      </c>
+      <c r="D63" s="12">
         <v>37</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="F63" s="12">
+      <c r="F63" s="13">
         <v>6</v>
       </c>
-      <c r="G63" s="10"/>
+      <c r="G63" s="11"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B64" s="9" t="s">
         <v>125</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D64" s="11">
+        <v>277</v>
+      </c>
+      <c r="D64" s="12">
         <v>37</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="F64" s="12">
+      <c r="F64" s="13">
         <v>0</v>
       </c>
-      <c r="G64" s="10"/>
+      <c r="G64" s="11"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>127</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D65" s="11">
+        <v>273</v>
+      </c>
+      <c r="D65" s="12">
         <v>42.300000000000004</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="F65" s="12">
+      <c r="F65" s="13">
         <v>0</v>
       </c>
-      <c r="G65" s="10"/>
+      <c r="G65" s="11"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B66" s="9" t="s">
         <v>129</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D66" s="11">
+        <v>273</v>
+      </c>
+      <c r="D66" s="12">
         <v>42.300000000000004</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="F66" s="12">
+      <c r="F66" s="13">
         <v>3</v>
       </c>
-      <c r="G66" s="10"/>
+      <c r="G66" s="11"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B67" s="9" t="s">
         <v>131</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D67" s="11">
+        <v>273</v>
+      </c>
+      <c r="D67" s="12">
         <v>42.300000000000004</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="F67" s="12">
+      <c r="F67" s="13">
         <v>3</v>
       </c>
-      <c r="G67" s="10"/>
+      <c r="G67" s="11"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B68" s="9" t="s">
         <v>133</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D68" s="11">
+        <v>276</v>
+      </c>
+      <c r="D68" s="12">
         <v>109.49000000000001</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="F68" s="12">
+      <c r="F68" s="13">
         <v>1</v>
       </c>
-      <c r="G68" s="10"/>
+      <c r="G68" s="11"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B69" s="9" t="s">
         <v>135</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D69" s="11">
+        <v>276</v>
+      </c>
+      <c r="D69" s="12">
         <v>96.850000000000009</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="F69" s="12">
+      <c r="F69" s="13">
         <v>2</v>
       </c>
-      <c r="G69" s="10"/>
+      <c r="G69" s="11"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B70" s="9" t="s">
         <v>137</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D70" s="11">
+        <v>276</v>
+      </c>
+      <c r="D70" s="12">
         <v>96.850000000000009</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="F70" s="12">
+      <c r="F70" s="13">
         <v>2</v>
       </c>
-      <c r="G70" s="10"/>
+      <c r="G70" s="11"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B71" s="9" t="s">
         <v>139</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D71" s="11">
+        <v>277</v>
+      </c>
+      <c r="D71" s="12">
         <v>37</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="F71" s="12">
-        <v>-1</v>
-      </c>
-      <c r="G71" s="10"/>
+      <c r="F71" s="13">
+        <v>-3</v>
+      </c>
+      <c r="G71" s="11"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B72" s="9" t="s">
         <v>141</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D72" s="11">
+        <v>277</v>
+      </c>
+      <c r="D72" s="12">
         <v>34</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="F72" s="12">
+      <c r="F72" s="13">
         <v>1</v>
       </c>
-      <c r="G72" s="10"/>
+      <c r="G72" s="11"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B73" s="9" t="s">
         <v>143</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D73" s="11">
+        <v>277</v>
+      </c>
+      <c r="D73" s="12">
         <v>34</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="F73" s="12">
+      <c r="F73" s="13">
         <v>2</v>
       </c>
-      <c r="G73" s="10"/>
+      <c r="G73" s="11"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B74" s="9" t="s">
         <v>145</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D74" s="11">
+        <v>273</v>
+      </c>
+      <c r="D74" s="12">
         <v>46.5</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F74" s="12">
-        <v>2</v>
-      </c>
-      <c r="G74" s="10"/>
+      <c r="F74" s="13">
+        <v>1</v>
+      </c>
+      <c r="G74" s="11"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B75" s="9" t="s">
         <v>147</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D75" s="11">
+        <v>273</v>
+      </c>
+      <c r="D75" s="12">
         <v>60</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="F75" s="12">
+      <c r="F75" s="13">
         <v>1</v>
       </c>
-      <c r="G75" s="10"/>
+      <c r="G75" s="11"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B76" s="9" t="s">
         <v>149</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D76" s="11">
+        <v>273</v>
+      </c>
+      <c r="D76" s="12">
         <v>60</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="F76" s="12">
+      <c r="F76" s="13">
         <v>7</v>
       </c>
-      <c r="G76" s="10"/>
+      <c r="G76" s="11"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B77" s="9" t="s">
         <v>151</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D77" s="11">
+        <v>276</v>
+      </c>
+      <c r="D77" s="12">
         <v>136</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="F77" s="12">
+      <c r="F77" s="13">
         <v>1</v>
       </c>
-      <c r="G77" s="10"/>
+      <c r="G77" s="11"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B78" s="9" t="s">
         <v>153</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D78" s="11">
+        <v>276</v>
+      </c>
+      <c r="D78" s="12">
         <v>136</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F78" s="12">
+      <c r="F78" s="13">
         <v>2</v>
       </c>
-      <c r="G78" s="10"/>
+      <c r="G78" s="11"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B79" s="9" t="s">
         <v>155</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D79" s="11">
+        <v>276</v>
+      </c>
+      <c r="D79" s="12">
         <v>136</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="F79" s="12">
+      <c r="F79" s="13">
         <v>-1</v>
       </c>
-      <c r="G79" s="10"/>
+      <c r="G79" s="11"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B80" s="9" t="s">
         <v>157</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D80" s="11">
+        <v>273</v>
+      </c>
+      <c r="D80" s="12">
         <v>53</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="F80" s="12">
+      <c r="F80" s="13">
         <v>4</v>
       </c>
-      <c r="G80" s="10"/>
+      <c r="G80" s="11"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B81" s="9" t="s">
         <v>159</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D81" s="11">
+        <v>273</v>
+      </c>
+      <c r="D81" s="12">
         <v>53</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="F81" s="12">
-        <v>1</v>
-      </c>
-      <c r="G81" s="10"/>
+      <c r="F81" s="13">
+        <v>0</v>
+      </c>
+      <c r="G81" s="11"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B82" s="9" t="s">
         <v>161</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D82" s="11">
+        <v>276</v>
+      </c>
+      <c r="D82" s="12">
         <v>123</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="F82" s="12">
+      <c r="F82" s="13">
         <v>3</v>
       </c>
-      <c r="G82" s="10"/>
+      <c r="G82" s="11"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B83" s="9" t="s">
         <v>163</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D83" s="11">
+        <v>276</v>
+      </c>
+      <c r="D83" s="12">
         <v>123</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="F83" s="12">
+      <c r="F83" s="13">
         <v>3</v>
       </c>
-      <c r="G83" s="10"/>
+      <c r="G83" s="11"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B84" s="9" t="s">
         <v>165</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="D84" s="11">
+        <v>285</v>
+      </c>
+      <c r="D84" s="12">
         <v>36</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="F84" s="12">
+      <c r="F84" s="13">
         <v>3</v>
       </c>
-      <c r="G84" s="10"/>
+      <c r="G84" s="11"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B85" s="9" t="s">
         <v>165</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D85" s="11">
+        <v>274</v>
+      </c>
+      <c r="D85" s="12">
         <v>107</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="F85" s="12">
+      <c r="F85" s="13">
         <v>3</v>
       </c>
-      <c r="G85" s="10"/>
+      <c r="G85" s="11"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B86" s="9" t="s">
         <v>168</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D86" s="11">
+        <v>273</v>
+      </c>
+      <c r="D86" s="12">
         <v>39.5</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="F86" s="12">
+      <c r="F86" s="13">
         <v>2</v>
       </c>
-      <c r="G86" s="10"/>
+      <c r="G86" s="11"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B87" s="9" t="s">
         <v>170</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D87" s="11">
+        <v>273</v>
+      </c>
+      <c r="D87" s="12">
         <v>39.5</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="F87" s="12">
+      <c r="F87" s="13">
         <v>2</v>
       </c>
-      <c r="G87" s="10"/>
+      <c r="G87" s="11"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B88" s="9" t="s">
         <v>172</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D88" s="11">
+        <v>276</v>
+      </c>
+      <c r="D88" s="12">
         <v>90</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="F88" s="12">
+      <c r="F88" s="13">
         <v>2</v>
       </c>
-      <c r="G88" s="10"/>
+      <c r="G88" s="11"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B89" s="9" t="s">
         <v>174</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D89" s="11">
+        <v>276</v>
+      </c>
+      <c r="D89" s="12">
         <v>86</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="F89" s="12">
-        <v>3</v>
-      </c>
-      <c r="G89" s="10"/>
+      <c r="F89" s="13">
+        <v>2</v>
+      </c>
+      <c r="G89" s="11"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B90" s="9" t="s">
         <v>176</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D90" s="11">
+        <v>275</v>
+      </c>
+      <c r="D90" s="12">
         <v>130</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="F90" s="12">
+      <c r="F90" s="13">
         <v>1</v>
       </c>
-      <c r="G90" s="10"/>
+      <c r="G90" s="11"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B91" s="9" t="s">
         <v>178</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D91" s="11">
+        <v>275</v>
+      </c>
+      <c r="D91" s="12">
         <v>130</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="F91" s="12">
+      <c r="F91" s="13">
         <v>2</v>
       </c>
-      <c r="G91" s="10"/>
+      <c r="G91" s="11"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B92" s="9" t="s">
         <v>180</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D92" s="11">
+        <v>273</v>
+      </c>
+      <c r="D92" s="12">
         <v>34.5</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="F92" s="12">
+      <c r="F92" s="13">
         <v>1</v>
       </c>
-      <c r="G92" s="10"/>
+      <c r="G92" s="11"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B93" s="9" t="s">
         <v>182</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D93" s="11">
+        <v>274</v>
+      </c>
+      <c r="D93" s="12">
         <v>71.5</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F93" s="12">
+      <c r="F93" s="13">
         <v>0</v>
       </c>
-      <c r="G93" s="10"/>
+      <c r="G93" s="11"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B94" s="9" t="s">
         <v>184</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D94" s="11">
+        <v>281</v>
+      </c>
+      <c r="D94" s="12">
         <v>131.5</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="F94" s="12">
+      <c r="F94" s="13">
         <v>0</v>
       </c>
-      <c r="G94" s="10"/>
+      <c r="G94" s="11"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B95" s="9" t="s">
         <v>186</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D95" s="11">
+        <v>273</v>
+      </c>
+      <c r="D95" s="12">
         <v>36</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="F95" s="12">
+      <c r="F95" s="13">
         <v>3</v>
       </c>
-      <c r="G95" s="10"/>
+      <c r="G95" s="11"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B96" s="9" t="s">
         <v>188</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D96" s="11">
+        <v>273</v>
+      </c>
+      <c r="D96" s="12">
         <v>36</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="F96" s="12">
+      <c r="F96" s="13">
         <v>1</v>
       </c>
-      <c r="G96" s="10"/>
+      <c r="G96" s="11"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B97" s="9" t="s">
         <v>190</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D97" s="11">
+        <v>276</v>
+      </c>
+      <c r="D97" s="12">
         <v>78</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="F97" s="12">
+      <c r="F97" s="13">
         <v>3</v>
       </c>
-      <c r="G97" s="10"/>
+      <c r="G97" s="11"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B98" s="9" t="s">
         <v>192</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D98" s="11">
+        <v>276</v>
+      </c>
+      <c r="D98" s="12">
         <v>78</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="F98" s="12">
+      <c r="F98" s="13">
         <v>2</v>
       </c>
-      <c r="G98" s="10"/>
+      <c r="G98" s="11"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B99" s="9" t="s">
         <v>194</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D99" s="11">
+        <v>275</v>
+      </c>
+      <c r="D99" s="12">
         <v>150</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="F99" s="12">
+      <c r="F99" s="13">
         <v>2</v>
       </c>
-      <c r="G99" s="10"/>
+      <c r="G99" s="11"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B100" s="9" t="s">
         <v>196</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D100" s="11">
+        <v>275</v>
+      </c>
+      <c r="D100" s="12">
         <v>150</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="F100" s="12">
+      <c r="F100" s="13">
         <v>2</v>
       </c>
-      <c r="G100" s="10"/>
+      <c r="G100" s="11"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B101" s="9" t="s">
         <v>198</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D101" s="11">
-        <v>55</v>
+        <v>274</v>
+      </c>
+      <c r="D101" s="12">
+        <v>71</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="F101" s="12">
+      <c r="F101" s="13">
         <v>0</v>
       </c>
-      <c r="G101" s="10"/>
+      <c r="G101" s="11"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B102" s="9" t="s">
         <v>200</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D102" s="11">
+        <v>280</v>
+      </c>
+      <c r="D102" s="12">
         <v>35.5</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="F102" s="12">
-        <v>6</v>
-      </c>
-      <c r="G102" s="10"/>
+      <c r="F102" s="13">
+        <v>30</v>
+      </c>
+      <c r="G102" s="11"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B103" s="9" t="s">
         <v>202</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D103" s="11">
+        <v>280</v>
+      </c>
+      <c r="D103" s="12">
         <v>35.5</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="F103" s="12">
+      <c r="F103" s="13">
         <v>0</v>
       </c>
-      <c r="G103" s="10"/>
+      <c r="G103" s="11"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B104" s="9" t="s">
         <v>204</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D104" s="11">
+        <v>280</v>
+      </c>
+      <c r="D104" s="12">
         <v>35.5</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="F104" s="12">
+      <c r="F104" s="13">
         <v>4</v>
       </c>
-      <c r="G104" s="10"/>
+      <c r="G104" s="11"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B105" s="9" t="s">
         <v>206</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D105" s="11">
-        <v>53.95</v>
+        <v>273</v>
+      </c>
+      <c r="D105" s="12">
+        <v>64</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="F105" s="12">
-        <v>0</v>
-      </c>
-      <c r="G105" s="10"/>
+      <c r="F105" s="13">
+        <v>5</v>
+      </c>
+      <c r="G105" s="11"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B106" s="9" t="s">
         <v>208</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D106" s="11">
+        <v>273</v>
+      </c>
+      <c r="D106" s="12">
         <v>64</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="F106" s="12">
-        <v>8</v>
-      </c>
-      <c r="G106" s="10"/>
+      <c r="F106" s="13">
+        <v>3</v>
+      </c>
+      <c r="G106" s="11"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B107" s="9" t="s">
         <v>210</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D107" s="11">
-        <v>53.95</v>
+        <v>274</v>
+      </c>
+      <c r="D107" s="12">
+        <v>146</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F107" s="12">
-        <v>3</v>
-      </c>
-      <c r="G107" s="10"/>
+      <c r="F107" s="13">
+        <v>0</v>
+      </c>
+      <c r="G107" s="11"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B108" s="9" t="s">
         <v>212</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D108" s="11">
+        <v>274</v>
+      </c>
+      <c r="D108" s="12">
         <v>146</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="F108" s="12">
-        <v>0</v>
-      </c>
-      <c r="G108" s="10"/>
+      <c r="F108" s="13">
+        <v>7</v>
+      </c>
+      <c r="G108" s="11"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B109" s="9" t="s">
         <v>214</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D109" s="11">
+        <v>274</v>
+      </c>
+      <c r="D109" s="12">
         <v>146</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="F109" s="12">
-        <v>2</v>
-      </c>
-      <c r="G109" s="10"/>
+      <c r="F109" s="13">
+        <v>1</v>
+      </c>
+      <c r="G109" s="11"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B110" s="9" t="s">
         <v>216</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D110" s="11">
-        <v>146</v>
+        <v>277</v>
+      </c>
+      <c r="D110" s="12">
+        <v>20.5</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="F110" s="12">
-        <v>1</v>
-      </c>
-      <c r="G110" s="10"/>
+      <c r="F110" s="13">
+        <v>4</v>
+      </c>
+      <c r="G110" s="11"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B111" s="9" t="s">
         <v>218</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D111" s="11">
-        <v>20.5</v>
+        <v>273</v>
+      </c>
+      <c r="D111" s="12">
+        <v>34.15</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="F111" s="12">
-        <v>4</v>
-      </c>
-      <c r="G111" s="10"/>
+      <c r="F111" s="13">
+        <v>1</v>
+      </c>
+      <c r="G111" s="11"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B112" s="9" t="s">
         <v>220</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D112" s="11">
+        <v>273</v>
+      </c>
+      <c r="D112" s="12">
         <v>34.15</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="F112" s="12">
+      <c r="F112" s="13">
         <v>1</v>
       </c>
-      <c r="G112" s="10"/>
+      <c r="G112" s="11"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B113" s="9" t="s">
         <v>222</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D113" s="11">
-        <v>34.15</v>
+        <v>276</v>
+      </c>
+      <c r="D113" s="12">
+        <v>76.350000000000009</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="F113" s="12">
-        <v>1</v>
-      </c>
-      <c r="G113" s="10"/>
+      <c r="F113" s="13">
+        <v>2</v>
+      </c>
+      <c r="G113" s="11"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>303</v>
-      </c>
       <c r="B114" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="C114" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D114" s="11">
-        <v>76.350000000000009</v>
+      <c r="D114" s="12">
+        <v>6.55</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="F114" s="12">
-        <v>2</v>
-      </c>
-      <c r="G114" s="10"/>
+      <c r="F114" s="13">
+        <v>0</v>
+      </c>
+      <c r="G114" s="11"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B115" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="D115" s="11">
-        <v>6.55</v>
+      <c r="C115" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D115" s="12">
+        <v>10</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F115" s="12">
-        <v>0</v>
-      </c>
-      <c r="G115" s="10"/>
+      <c r="F115" s="13">
+        <v>6</v>
+      </c>
+      <c r="G115" s="11"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B116" s="9" t="s">
         <v>228</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D116" s="11">
-        <v>10</v>
+        <v>278</v>
+      </c>
+      <c r="D116" s="12">
+        <v>8.5</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="F116" s="12">
-        <v>8</v>
-      </c>
-      <c r="G116" s="10"/>
+      <c r="F116" s="13">
+        <v>1</v>
+      </c>
+      <c r="G116" s="11"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B117" s="9" t="s">
         <v>230</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D117" s="11">
-        <v>8.5</v>
+        <v>278</v>
+      </c>
+      <c r="D117" s="12">
+        <v>10</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F117" s="12">
-        <v>1</v>
-      </c>
-      <c r="G117" s="10"/>
+      <c r="F117" s="13">
+        <v>0</v>
+      </c>
+      <c r="G117" s="11"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>302</v>
+      </c>
       <c r="B118" s="9" t="s">
         <v>232</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D118" s="11">
-        <v>10</v>
+        <v>273</v>
+      </c>
+      <c r="D118" s="12">
+        <v>46.35</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="F118" s="12">
-        <v>2</v>
-      </c>
-      <c r="G118" s="10"/>
+      <c r="F118" s="13">
+        <v>3</v>
+      </c>
+      <c r="G118" s="11"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B119" s="9" t="s">
         <v>234</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D119" s="11">
+        <v>273</v>
+      </c>
+      <c r="D119" s="12">
         <v>46.35</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="F119" s="12">
-        <v>3</v>
-      </c>
-      <c r="G119" s="10"/>
+      <c r="F119" s="13">
+        <v>2</v>
+      </c>
+      <c r="G119" s="11"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B120" s="9" t="s">
         <v>236</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D120" s="11">
-        <v>46.35</v>
+        <v>276</v>
+      </c>
+      <c r="D120" s="12">
+        <v>107.35000000000001</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="F120" s="12">
+      <c r="F120" s="13">
         <v>2</v>
       </c>
-      <c r="G120" s="10"/>
+      <c r="G120" s="11"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="B121" s="9" t="s">
         <v>238</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D121" s="11">
-        <v>107.35000000000001</v>
+        <v>273</v>
+      </c>
+      <c r="D121" s="12">
+        <v>52</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F121" s="12">
+      <c r="F121" s="13">
         <v>2</v>
       </c>
-      <c r="G121" s="10"/>
+      <c r="G121" s="11"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B122" s="9" t="s">
         <v>240</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D122" s="11">
+        <v>273</v>
+      </c>
+      <c r="D122" s="12">
         <v>52</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="F122" s="12">
-        <v>2</v>
-      </c>
-      <c r="G122" s="10"/>
+      <c r="F122" s="13">
+        <v>0</v>
+      </c>
+      <c r="G122" s="11"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B123" s="9" t="s">
         <v>242</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D123" s="11">
-        <v>52</v>
+        <v>273</v>
+      </c>
+      <c r="D123" s="12">
+        <v>55</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="F123" s="12">
-        <v>0</v>
-      </c>
-      <c r="G123" s="10"/>
+      <c r="F123" s="13">
+        <v>3</v>
+      </c>
+      <c r="G123" s="11"/>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B124" s="9" t="s">
         <v>244</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D124" s="11">
-        <v>55</v>
+        <v>282</v>
+      </c>
+      <c r="D124" s="12">
+        <v>95.990000000000009</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="F124" s="12">
-        <v>4</v>
-      </c>
-      <c r="G124" s="10"/>
+      <c r="F124" s="13">
+        <v>2</v>
+      </c>
+      <c r="G124" s="11"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B125" s="9" t="s">
         <v>246</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D125" s="11">
-        <v>95.990000000000009</v>
+        <v>282</v>
+      </c>
+      <c r="D125" s="12">
+        <v>114.49000000000001</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="F125" s="12">
-        <v>3</v>
-      </c>
-      <c r="G125" s="10"/>
+      <c r="F125" s="13">
+        <v>2</v>
+      </c>
+      <c r="G125" s="11"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B126" s="9" t="s">
         <v>248</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D126" s="11">
-        <v>114.49000000000001</v>
+        <v>282</v>
+      </c>
+      <c r="D126" s="12">
+        <v>95.990000000000009</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="F126" s="12">
-        <v>2</v>
-      </c>
-      <c r="G126" s="10"/>
+      <c r="F126" s="13">
+        <v>1</v>
+      </c>
+      <c r="G126" s="11"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B127" s="9" t="s">
         <v>250</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D127" s="11">
-        <v>95.990000000000009</v>
+        <v>275</v>
+      </c>
+      <c r="D127" s="12">
+        <v>225</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="F127" s="12">
-        <v>1</v>
-      </c>
-      <c r="G127" s="10"/>
+      <c r="F127" s="13">
+        <v>3</v>
+      </c>
+      <c r="G127" s="11"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B128" s="9" t="s">
         <v>252</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D128" s="11">
+        <v>275</v>
+      </c>
+      <c r="D128" s="12">
         <v>212</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="F128" s="12">
-        <v>2</v>
-      </c>
-      <c r="G128" s="10"/>
+      <c r="F128" s="13">
+        <v>3</v>
+      </c>
+      <c r="G128" s="11"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B129" s="9" t="s">
         <v>254</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D129" s="11">
+        <v>275</v>
+      </c>
+      <c r="D129" s="12">
         <v>212</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="F129" s="12">
-        <v>3</v>
-      </c>
-      <c r="G129" s="10"/>
+      <c r="F129" s="13">
+        <v>0</v>
+      </c>
+      <c r="G129" s="11"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
-        <v>298</v>
-      </c>
       <c r="B130" s="9" t="s">
         <v>256</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D130" s="11">
-        <v>212</v>
+        <v>283</v>
+      </c>
+      <c r="D130" s="12">
+        <v>40</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="F130" s="12">
-        <v>0</v>
-      </c>
-      <c r="G130" s="10"/>
+      <c r="F130" s="13">
+        <v>2</v>
+      </c>
+      <c r="G130" s="11"/>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B131" s="9" t="s">
         <v>258</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="D131" s="11">
-        <v>40</v>
+        <v>282</v>
+      </c>
+      <c r="D131" s="12">
+        <v>86</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="F131" s="12">
-        <v>2</v>
-      </c>
-      <c r="G131" s="10"/>
+      <c r="F131" s="13">
+        <v>0</v>
+      </c>
+      <c r="G131" s="11"/>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B132" s="9" t="s">
         <v>260</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D132" s="11">
-        <v>86</v>
+        <v>282</v>
+      </c>
+      <c r="D132" s="12">
+        <v>108.31</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="F132" s="12">
-        <v>0</v>
-      </c>
-      <c r="G132" s="10"/>
+      <c r="F132" s="13">
+        <v>1</v>
+      </c>
+      <c r="G132" s="11"/>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B133" s="9" t="s">
         <v>262</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D133" s="11">
-        <v>108.31</v>
+        <v>282</v>
+      </c>
+      <c r="D133" s="12">
+        <v>73.650000000000006</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="F133" s="12">
-        <v>1</v>
-      </c>
-      <c r="G133" s="10"/>
+      <c r="F133" s="13">
+        <v>2</v>
+      </c>
+      <c r="G133" s="11"/>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B134" s="9" t="s">
@@ -4146,51 +4140,38 @@
       <c r="C134" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D134" s="11">
-        <v>73.650000000000006</v>
+      <c r="D134" s="12">
+        <v>190</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F134" s="12">
-        <v>2</v>
-      </c>
-      <c r="G134" s="10"/>
+      <c r="F134" s="13">
+        <v>1</v>
+      </c>
+      <c r="G134" s="11"/>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B135" s="9" t="s">
         <v>266</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D135" s="11">
-        <v>190</v>
+        <v>276</v>
+      </c>
+      <c r="D135" s="12">
+        <v>67</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="F135" s="12">
+      <c r="F135" s="13">
         <v>1</v>
       </c>
-      <c r="G135" s="10"/>
+      <c r="G135" s="11"/>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B136" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D136" s="11">
-        <v>67</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="F136" s="12">
-        <v>1</v>
-      </c>
+      <c r="E136" s="2"/>
+      <c r="F136" s="5"/>
       <c r="G136" s="10"/>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
@@ -5011,7 +4992,6 @@
     <row r="300" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E300" s="2"/>
       <c r="F300" s="5"/>
-      <c r="G300" s="10"/>
     </row>
     <row r="301" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E301" s="2"/>
@@ -5584,10 +5564,6 @@
     <row r="443" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E443" s="2"/>
       <c r="F443" s="5"/>
-    </row>
-    <row r="444" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E444" s="2"/>
-      <c r="F444" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
